--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE20"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1108,7 +1108,7 @@
       <c r="C4" s="1" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-iso-xx246877</t>
+          <t>kassbohrer-maxima-shtor-00116344</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -1125,13 +1125,14 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп изотермический Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска пневматическая, тормоза барабанные.
-Грузоподъёмность 31 290 кг.
-Длина кузова 13,7 м, объём 94 м³.
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
+Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
-Возможна аренда — уточняйте условия по телефону.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.
 Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
@@ -1142,14 +1143,14 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-10.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1179,7 +1180,7 @@
       <c r="AA4" s="1" t="inlineStr"/>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
@@ -1224,19 +1225,19 @@
       </c>
       <c r="AS4" s="1" t="inlineStr">
         <is>
-          <t>Изотермический</t>
+          <t>Шторный</t>
         </is>
       </c>
       <c r="AT4" s="1" t="inlineStr"/>
       <c r="AU4" s="1" t="inlineStr"/>
       <c r="AV4" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF10300124805</t>
+          <t>WKVDAF30300116344</t>
         </is>
       </c>
       <c r="AW4" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="AX4" s="1" t="inlineStr">
@@ -1246,27 +1247,27 @@
       </c>
       <c r="AY4" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ4" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA4" s="1" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="BB4" s="1" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="BC4" s="1" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>110.6</t>
         </is>
       </c>
       <c r="BD4" s="1" t="inlineStr"/>
@@ -1282,7 +1283,7 @@
       <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00116344</t>
+          <t>kassbohrer-maxima-shtor-00124397</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -1299,7 +1300,7 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
 Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
 Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
 Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
@@ -1317,14 +1318,14 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-04.jpg</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1354,7 +1355,7 @@
       <c r="AA5" s="1" t="inlineStr"/>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
@@ -1406,12 +1407,12 @@
       <c r="AU5" s="1" t="inlineStr"/>
       <c r="AV5" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300116344</t>
+          <t>WKVDAF30300124397</t>
         </is>
       </c>
       <c r="AW5" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX5" s="1" t="inlineStr">
@@ -1457,7 +1458,7 @@
       <c r="C6" s="1" t="inlineStr"/>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00124397</t>
+          <t>kassbohrer-maxima-shtor-00124732</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -1474,11 +1475,11 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
-Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
+          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
+Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.
@@ -1492,14 +1493,14 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>3290000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-04.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-06.jpg</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr"/>
@@ -1529,7 +1530,7 @@
       <c r="AA6" s="1" t="inlineStr"/>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>3290000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
@@ -1581,7 +1582,7 @@
       <c r="AU6" s="1" t="inlineStr"/>
       <c r="AV6" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300124397</t>
+          <t>WKVDAF30300124732</t>
         </is>
       </c>
       <c r="AW6" s="1" t="inlineStr">
@@ -1601,7 +1602,7 @@
       </c>
       <c r="AZ6" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA6" s="1" t="inlineStr">
@@ -1611,12 +1612,12 @@
       </c>
       <c r="BB6" s="1" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC6" s="1" t="inlineStr">
         <is>
-          <t>110.6</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BD6" s="1" t="inlineStr"/>
@@ -1632,7 +1633,7 @@
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00124732</t>
+          <t>steelbear-pf41n-v000319</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -1649,15 +1650,12 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
-Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
+Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
+Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
+При покупке в лизинг — скидка от Минпромторга 10%.
+Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1667,14 +1665,14 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1704,15 +1702,19 @@
       <c r="AA7" s="1" t="inlineStr"/>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD7" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD7" s="1" t="inlineStr">
+        <is>
+          <t>325000</t>
+        </is>
+      </c>
       <c r="AE7" s="1" t="inlineStr"/>
       <c r="AF7" s="1" t="inlineStr"/>
       <c r="AG7" s="1" t="inlineStr"/>
@@ -1723,7 +1725,7 @@
       <c r="AL7" s="1" t="inlineStr"/>
       <c r="AM7" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN7" s="1" t="inlineStr"/>
@@ -1734,12 +1736,12 @@
       </c>
       <c r="AP7" s="1" t="inlineStr">
         <is>
-          <t>Kassbohrer</t>
+          <t>Steelbear</t>
         </is>
       </c>
       <c r="AQ7" s="1" t="inlineStr">
         <is>
-          <t>Maxima</t>
+          <t>PF-41N</t>
         </is>
       </c>
       <c r="AR7" s="1" t="inlineStr">
@@ -1749,51 +1751,43 @@
       </c>
       <c r="AS7" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT7" s="1" t="inlineStr"/>
       <c r="AU7" s="1" t="inlineStr"/>
-      <c r="AV7" s="1" t="inlineStr">
-        <is>
-          <t>WKVDAF30300124732</t>
-        </is>
-      </c>
+      <c r="AV7" s="1" t="inlineStr"/>
       <c r="AW7" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX7" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY7" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ7" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA7" s="1" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="BB7" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC7" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="BC7" s="1" t="inlineStr"/>
       <c r="BD7" s="1" t="inlineStr"/>
       <c r="BE7" s="1" t="inlineStr"/>
     </row>
@@ -1807,7 +1801,7 @@
       <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pf41n-v000319</t>
+          <t>steelbear-pl24l-avg36</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -1824,12 +1818,13 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
-Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
-Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L Fox), 3-х осный, под заказ.
+Осевой агрегат Fox, барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
+6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
+Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
 При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
+Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1839,14 +1834,14 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1876,7 +1871,7 @@
       <c r="AA8" s="1" t="inlineStr"/>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1886,7 +1881,7 @@
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>296000</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr"/>
@@ -1915,7 +1910,7 @@
       </c>
       <c r="AQ8" s="1" t="inlineStr">
         <is>
-          <t>PF-41N</t>
+          <t>PL-24L</t>
         </is>
       </c>
       <c r="AR8" s="1" t="inlineStr">
@@ -1925,7 +1920,7 @@
       </c>
       <c r="AS8" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT8" s="1" t="inlineStr"/>
@@ -1938,7 +1933,7 @@
       </c>
       <c r="AX8" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY8" s="1" t="inlineStr">
@@ -1948,17 +1943,17 @@
       </c>
       <c r="AZ8" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA8" s="1" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="BB8" s="1" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="BC8" s="1" t="inlineStr"/>
@@ -1975,7 +1970,7 @@
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-avg36</t>
+          <t>steelbear-pl24l-ea653666</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -1992,13 +1987,13 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L Fox), 3-х осный, под заказ.
-Осевой агрегат Fox, барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
-6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
-Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
-При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
+Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -2008,14 +2003,14 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>2960000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2045,19 +2040,15 @@
       <c r="AA9" s="1" t="inlineStr"/>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>2960000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD9" s="1" t="inlineStr">
-        <is>
-          <t>296000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD9" s="1" t="inlineStr"/>
       <c r="AE9" s="1" t="inlineStr"/>
       <c r="AF9" s="1" t="inlineStr"/>
       <c r="AG9" s="1" t="inlineStr"/>
@@ -2068,7 +2059,7 @@
       <c r="AL9" s="1" t="inlineStr"/>
       <c r="AM9" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN9" s="1" t="inlineStr"/>
@@ -2099,10 +2090,14 @@
       </c>
       <c r="AT9" s="1" t="inlineStr"/>
       <c r="AU9" s="1" t="inlineStr"/>
-      <c r="AV9" s="1" t="inlineStr"/>
+      <c r="AV9" s="1" t="inlineStr">
+        <is>
+          <t>XWZ9412LLR1202021</t>
+        </is>
+      </c>
       <c r="AW9" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX9" s="1" t="inlineStr">
@@ -2122,7 +2117,7 @@
       </c>
       <c r="BA9" s="1" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="BB9" s="1" t="inlineStr">
@@ -2144,7 +2139,7 @@
       <c r="C10" s="1" t="inlineStr"/>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>tonar-b313-9888</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -2161,13 +2156,12 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
-Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
+Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
+Итоговая цена при лизинге: 2 520 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -2177,14 +2171,14 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2214,17 +2208,25 @@
       <c r="AA10" s="1" t="inlineStr"/>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD10" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD10" s="1" t="inlineStr">
+        <is>
+          <t>315000</t>
+        </is>
+      </c>
       <c r="AE10" s="1" t="inlineStr"/>
-      <c r="AF10" s="1" t="inlineStr"/>
+      <c r="AF10" s="1" t="inlineStr">
+        <is>
+          <t>315000</t>
+        </is>
+      </c>
       <c r="AG10" s="1" t="inlineStr"/>
       <c r="AH10" s="1" t="inlineStr"/>
       <c r="AI10" s="1" t="inlineStr"/>
@@ -2233,7 +2235,7 @@
       <c r="AL10" s="1" t="inlineStr"/>
       <c r="AM10" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN10" s="1" t="inlineStr"/>
@@ -2244,12 +2246,12 @@
       </c>
       <c r="AP10" s="1" t="inlineStr">
         <is>
-          <t>Steelbear</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ10" s="1" t="inlineStr">
         <is>
-          <t>PL-24L</t>
+          <t>B3-13 (9888)</t>
         </is>
       </c>
       <c r="AR10" s="1" t="inlineStr">
@@ -2259,19 +2261,15 @@
       </c>
       <c r="AS10" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Бортовой</t>
         </is>
       </c>
       <c r="AT10" s="1" t="inlineStr"/>
       <c r="AU10" s="1" t="inlineStr"/>
-      <c r="AV10" s="1" t="inlineStr">
-        <is>
-          <t>XWZ9412LLR1202021</t>
-        </is>
-      </c>
+      <c r="AV10" s="1" t="inlineStr"/>
       <c r="AW10" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX10" s="1" t="inlineStr">
@@ -2291,12 +2289,12 @@
       </c>
       <c r="BA10" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="BB10" s="1" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC10" s="1" t="inlineStr"/>
@@ -2313,7 +2311,7 @@
       <c r="C11" s="1" t="inlineStr"/>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>tonar-b313-9888</t>
+          <t>tonar-k4u-99891-order</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -2330,12 +2328,13 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
-Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
-Итоговая цена при лизинге: 2 520 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
+(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -2345,14 +2344,14 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr"/>
@@ -2382,7 +2381,7 @@
       <c r="AA11" s="1" t="inlineStr"/>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -2392,13 +2391,13 @@
       </c>
       <c r="AD11" s="1" t="inlineStr">
         <is>
-          <t>315000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="AE11" s="1" t="inlineStr"/>
       <c r="AF11" s="1" t="inlineStr">
         <is>
-          <t>315000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="AG11" s="1" t="inlineStr"/>
@@ -2425,7 +2424,7 @@
       </c>
       <c r="AQ11" s="1" t="inlineStr">
         <is>
-          <t>B3-13 (9888)</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR11" s="1" t="inlineStr">
@@ -2435,7 +2434,7 @@
       </c>
       <c r="AS11" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT11" s="1" t="inlineStr"/>
@@ -2448,7 +2447,7 @@
       </c>
       <c r="AX11" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY11" s="1" t="inlineStr">
@@ -2463,12 +2462,12 @@
       </c>
       <c r="BA11" s="1" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="BB11" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="BC11" s="1" t="inlineStr"/>
@@ -2485,7 +2484,7 @@
       <c r="C12" s="1" t="inlineStr"/>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-99891-order</t>
+          <t>tonar-k4u-p0002033</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -2502,13 +2501,10 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
-(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2518,14 +2514,14 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
       <c r="S12" s="1" t="inlineStr"/>
@@ -2555,25 +2551,17 @@
       <c r="AA12" s="1" t="inlineStr"/>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="AC12" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD12" s="1" t="inlineStr">
-        <is>
-          <t>320000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD12" s="1" t="inlineStr"/>
       <c r="AE12" s="1" t="inlineStr"/>
-      <c r="AF12" s="1" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
+      <c r="AF12" s="1" t="inlineStr"/>
       <c r="AG12" s="1" t="inlineStr"/>
       <c r="AH12" s="1" t="inlineStr"/>
       <c r="AI12" s="1" t="inlineStr"/>
@@ -2582,7 +2570,7 @@
       <c r="AL12" s="1" t="inlineStr"/>
       <c r="AM12" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN12" s="1" t="inlineStr"/>
@@ -2613,10 +2601,14 @@
       </c>
       <c r="AT12" s="1" t="inlineStr"/>
       <c r="AU12" s="1" t="inlineStr"/>
-      <c r="AV12" s="1" t="inlineStr"/>
+      <c r="AV12" s="1" t="inlineStr">
+        <is>
+          <t>X0T998910P0002033</t>
+        </is>
+      </c>
       <c r="AW12" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX12" s="1" t="inlineStr">
@@ -2626,12 +2618,12 @@
       </c>
       <c r="AY12" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ12" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA12" s="1" t="inlineStr">
@@ -2641,7 +2633,7 @@
       </c>
       <c r="BB12" s="1" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="BC12" s="1" t="inlineStr"/>
@@ -2658,7 +2650,7 @@
       <c r="C13" s="1" t="inlineStr"/>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-p0002033</t>
+          <t>tonar-l3-9445</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
@@ -2675,10 +2667,12 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2688,14 +2682,14 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
         </is>
       </c>
       <c r="S13" s="1" t="inlineStr"/>
@@ -2725,17 +2719,25 @@
       <c r="AA13" s="1" t="inlineStr"/>
       <c r="AB13" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD13" s="1" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
       <c r="AE13" s="1" t="inlineStr"/>
-      <c r="AF13" s="1" t="inlineStr"/>
+      <c r="AF13" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
       <c r="AG13" s="1" t="inlineStr"/>
       <c r="AH13" s="1" t="inlineStr"/>
       <c r="AI13" s="1" t="inlineStr"/>
@@ -2744,7 +2746,7 @@
       <c r="AL13" s="1" t="inlineStr"/>
       <c r="AM13" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN13" s="1" t="inlineStr"/>
@@ -2760,7 +2762,7 @@
       </c>
       <c r="AQ13" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99891)</t>
+          <t>L3 (9445)</t>
         </is>
       </c>
       <c r="AR13" s="1" t="inlineStr">
@@ -2770,47 +2772,47 @@
       </c>
       <c r="AS13" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT13" s="1" t="inlineStr"/>
       <c r="AU13" s="1" t="inlineStr"/>
-      <c r="AV13" s="1" t="inlineStr">
-        <is>
-          <t>X0T998910P0002033</t>
-        </is>
-      </c>
+      <c r="AV13" s="1" t="inlineStr"/>
       <c r="AW13" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX13" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY13" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ13" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA13" s="1" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="BB13" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
-        </is>
-      </c>
-      <c r="BC13" s="1" t="inlineStr"/>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="BC13" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="BD13" s="1" t="inlineStr"/>
       <c r="BE13" s="1" t="inlineStr"/>
     </row>
@@ -2824,7 +2826,7 @@
       <c r="C14" s="1" t="inlineStr"/>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>tonar-l3-9445</t>
+          <t>tonar-reef-r313</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
@@ -2841,11 +2843,11 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
+          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
+В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
+Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 6 865 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -2856,14 +2858,14 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr"/>
@@ -2893,7 +2895,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
@@ -2903,15 +2905,11 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr"/>
-      <c r="AF14" s="1" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
+      <c r="AF14" s="1" t="inlineStr"/>
       <c r="AG14" s="1" t="inlineStr"/>
       <c r="AH14" s="1" t="inlineStr"/>
       <c r="AI14" s="1" t="inlineStr"/>
@@ -2936,7 +2934,7 @@
       </c>
       <c r="AQ14" s="1" t="inlineStr">
         <is>
-          <t>L3 (9445)</t>
+          <t>R3-13</t>
         </is>
       </c>
       <c r="AR14" s="1" t="inlineStr">
@@ -2946,7 +2944,7 @@
       </c>
       <c r="AS14" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="AT14" s="1" t="inlineStr"/>
@@ -2969,22 +2967,22 @@
       </c>
       <c r="AZ14" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA14" s="1" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>31200</t>
         </is>
       </c>
       <c r="BB14" s="1" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC14" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BD14" s="1" t="inlineStr"/>
@@ -3000,7 +2998,7 @@
       <c r="C15" s="1" t="inlineStr"/>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>tonar-reef-r313</t>
+          <t>tonar-samosval-9595</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -3017,11 +3015,10 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
-В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
-Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 6 865 000 ₽.
+          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
+Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
+Итоговая цена при лизинге: 3 780 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3032,14 +3029,14 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>4200000</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
         </is>
       </c>
       <c r="S15" s="1" t="inlineStr"/>
@@ -3069,7 +3066,7 @@
       <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>4200000</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -3079,7 +3076,7 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
@@ -3108,7 +3105,7 @@
       </c>
       <c r="AQ15" s="1" t="inlineStr">
         <is>
-          <t>R3-13</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="AR15" s="1" t="inlineStr">
@@ -3118,7 +3115,7 @@
       </c>
       <c r="AS15" s="1" t="inlineStr">
         <is>
-          <t>Рефрижератор</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AT15" s="1" t="inlineStr"/>
@@ -3131,7 +3128,7 @@
       </c>
       <c r="AX15" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY15" s="1" t="inlineStr">
@@ -3141,22 +3138,18 @@
       </c>
       <c r="AZ15" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA15" s="1" t="inlineStr">
         <is>
-          <t>31200</t>
-        </is>
-      </c>
-      <c r="BB15" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="BB15" s="1" t="inlineStr"/>
       <c r="BC15" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BD15" s="1" t="inlineStr"/>
@@ -3172,7 +3165,7 @@
       <c r="C16" s="1" t="inlineStr"/>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>tonar-samosval-9595</t>
+          <t>tonar-sdp489-95895</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
@@ -3189,10 +3182,11 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
-Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
-Итоговая цена при лизинге: 3 780 000 ₽.
+          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
+Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
+Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 7 150 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3203,14 +3197,14 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>4200000</t>
+          <t>7650000</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr"/>
@@ -3240,7 +3234,7 @@
       <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>4200000</t>
+          <t>7650000</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
@@ -3250,7 +3244,7 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>
@@ -3279,7 +3273,7 @@
       </c>
       <c r="AQ16" s="1" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>SDP4-89 (95895)</t>
         </is>
       </c>
       <c r="AR16" s="1" t="inlineStr">
@@ -3289,7 +3283,7 @@
       </c>
       <c r="AS16" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Щеповоз</t>
         </is>
       </c>
       <c r="AT16" s="1" t="inlineStr"/>
@@ -3312,18 +3306,22 @@
       </c>
       <c r="AZ16" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA16" s="1" t="inlineStr">
         <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="BB16" s="1" t="inlineStr"/>
+          <t>27800</t>
+        </is>
+      </c>
+      <c r="BB16" s="1" t="inlineStr">
+        <is>
+          <t>14600</t>
+        </is>
+      </c>
       <c r="BC16" s="1" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD16" s="1" t="inlineStr"/>
@@ -3339,7 +3337,7 @@
       <c r="C17" s="1" t="inlineStr"/>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>tonar-sdp489-95895</t>
+          <t>tonar-t313-9888</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr"/>
@@ -3356,11 +3354,11 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
-Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
-Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 7 150 000 ₽.
+          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
+Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
+Итоговая цена при лизинге: 3 040 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3371,14 +3369,14 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>7650000</t>
+          <t>3800000</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S17" s="1" t="inlineStr"/>
@@ -3408,7 +3406,7 @@
       <c r="AA17" s="1" t="inlineStr"/>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>7650000</t>
+          <t>3800000</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
@@ -3418,11 +3416,15 @@
       </c>
       <c r="AD17" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>380000</t>
         </is>
       </c>
       <c r="AE17" s="1" t="inlineStr"/>
-      <c r="AF17" s="1" t="inlineStr"/>
+      <c r="AF17" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
       <c r="AG17" s="1" t="inlineStr"/>
       <c r="AH17" s="1" t="inlineStr"/>
       <c r="AI17" s="1" t="inlineStr"/>
@@ -3447,7 +3449,7 @@
       </c>
       <c r="AQ17" s="1" t="inlineStr">
         <is>
-          <t>SDP4-89 (95895)</t>
+          <t>T3-13 (9888)</t>
         </is>
       </c>
       <c r="AR17" s="1" t="inlineStr">
@@ -3457,7 +3459,7 @@
       </c>
       <c r="AS17" s="1" t="inlineStr">
         <is>
-          <t>Щеповоз</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AT17" s="1" t="inlineStr"/>
@@ -3470,7 +3472,7 @@
       </c>
       <c r="AX17" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY17" s="1" t="inlineStr">
@@ -3485,17 +3487,17 @@
       </c>
       <c r="BA17" s="1" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="BB17" s="1" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC17" s="1" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD17" s="1" t="inlineStr"/>
@@ -3511,7 +3513,7 @@
       <c r="C18" s="1" t="inlineStr"/>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>tonar-t313-9888</t>
+          <t>tonar-zernovoz-95941</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
@@ -3528,11 +3530,10 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
-Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
-Итоговая цена при лизинге: 3 040 000 ₽.
+          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
+Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 4 900 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3543,14 +3544,14 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
         </is>
       </c>
       <c r="S18" s="1" t="inlineStr"/>
@@ -3580,7 +3581,7 @@
       <c r="AA18" s="1" t="inlineStr"/>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
@@ -3590,15 +3591,11 @@
       </c>
       <c r="AD18" s="1" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE18" s="1" t="inlineStr"/>
-      <c r="AF18" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
+      <c r="AF18" s="1" t="inlineStr"/>
       <c r="AG18" s="1" t="inlineStr"/>
       <c r="AH18" s="1" t="inlineStr"/>
       <c r="AI18" s="1" t="inlineStr"/>
@@ -3623,7 +3620,7 @@
       </c>
       <c r="AQ18" s="1" t="inlineStr">
         <is>
-          <t>T3-13 (9888)</t>
+          <t>95941</t>
         </is>
       </c>
       <c r="AR18" s="1" t="inlineStr">
@@ -3633,7 +3630,7 @@
       </c>
       <c r="AS18" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AT18" s="1" t="inlineStr"/>
@@ -3656,7 +3653,7 @@
       </c>
       <c r="AZ18" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA18" s="1" t="inlineStr">
@@ -3664,14 +3661,10 @@
           <t>31000</t>
         </is>
       </c>
-      <c r="BB18" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
+      <c r="BB18" s="1" t="inlineStr"/>
       <c r="BC18" s="1" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="BD18" s="1" t="inlineStr"/>
@@ -3687,7 +3680,7 @@
       <c r="C19" s="1" t="inlineStr"/>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>tonar-zernovoz-95941</t>
+          <t>v-trailer-329d-r0000119</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
@@ -3704,11 +3697,10 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
-Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 4 900 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -3718,14 +3710,14 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>2990000</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr"/>
@@ -3755,19 +3747,15 @@
       <c r="AA19" s="1" t="inlineStr"/>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>2990000</t>
         </is>
       </c>
       <c r="AC19" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD19" s="1" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD19" s="1" t="inlineStr"/>
       <c r="AE19" s="1" t="inlineStr"/>
       <c r="AF19" s="1" t="inlineStr"/>
       <c r="AG19" s="1" t="inlineStr"/>
@@ -3778,7 +3766,7 @@
       <c r="AL19" s="1" t="inlineStr"/>
       <c r="AM19" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN19" s="1" t="inlineStr"/>
@@ -3789,12 +3777,12 @@
       </c>
       <c r="AP19" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>V-Trailer</t>
         </is>
       </c>
       <c r="AQ19" s="1" t="inlineStr">
         <is>
-          <t>95941</t>
+          <t>329</t>
         </is>
       </c>
       <c r="AR19" s="1" t="inlineStr">
@@ -3804,15 +3792,19 @@
       </c>
       <c r="AS19" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Шторный</t>
         </is>
       </c>
       <c r="AT19" s="1" t="inlineStr"/>
       <c r="AU19" s="1" t="inlineStr"/>
-      <c r="AV19" s="1" t="inlineStr"/>
+      <c r="AV19" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
       <c r="AW19" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX19" s="1" t="inlineStr">
@@ -3827,192 +3819,26 @@
       </c>
       <c r="AZ19" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA19" s="1" t="inlineStr">
         <is>
-          <t>31000</t>
-        </is>
-      </c>
-      <c r="BB19" s="1" t="inlineStr"/>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB19" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
       <c r="BC19" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BD19" s="1" t="inlineStr"/>
       <c r="BE19" s="1" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15с2</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>v-trailer-329d-r0000119</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
-        </is>
-      </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>2990000</t>
-        </is>
-      </c>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
-        </is>
-      </c>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15с2</t>
-        </is>
-      </c>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr">
-        <is>
-          <t>Прицепы</t>
-        </is>
-      </c>
-      <c r="Y20" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="Z20" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AA20" s="1" t="inlineStr"/>
-      <c r="AB20" s="1" t="inlineStr">
-        <is>
-          <t>2990000</t>
-        </is>
-      </c>
-      <c r="AC20" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD20" s="1" t="inlineStr"/>
-      <c r="AE20" s="1" t="inlineStr"/>
-      <c r="AF20" s="1" t="inlineStr"/>
-      <c r="AG20" s="1" t="inlineStr"/>
-      <c r="AH20" s="1" t="inlineStr"/>
-      <c r="AI20" s="1" t="inlineStr"/>
-      <c r="AJ20" s="1" t="inlineStr"/>
-      <c r="AK20" s="1" t="inlineStr"/>
-      <c r="AL20" s="1" t="inlineStr"/>
-      <c r="AM20" s="1" t="inlineStr">
-        <is>
-          <t>С пробегом</t>
-        </is>
-      </c>
-      <c r="AN20" s="1" t="inlineStr"/>
-      <c r="AO20" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AP20" s="1" t="inlineStr">
-        <is>
-          <t>V-Trailer</t>
-        </is>
-      </c>
-      <c r="AQ20" s="1" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="AR20" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AS20" s="1" t="inlineStr">
-        <is>
-          <t>Шторный</t>
-        </is>
-      </c>
-      <c r="AT20" s="1" t="inlineStr"/>
-      <c r="AU20" s="1" t="inlineStr"/>
-      <c r="AV20" s="1" t="inlineStr">
-        <is>
-          <t>XZFVKRP3DR0000119</t>
-        </is>
-      </c>
-      <c r="AW20" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="AX20" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AY20" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
-      <c r="AZ20" s="1" t="inlineStr">
-        <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="BA20" s="1" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="BB20" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC20" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="BD20" s="1" t="inlineStr"/>
-      <c r="BE20" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2865,7 +2865,7 @@
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="AC2" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD2" s="1" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AC3" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD3" s="1" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AC4" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD4" s="1" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC5" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD5" s="1" t="inlineStr"/>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AC6" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD6" s="1" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AC12" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD12" s="1" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AC19" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD19" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2865,7 +2865,7 @@
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2865,7 +2865,7 @@
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE19"/>
+  <dimension ref="A1:BE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1633,7 +1633,7 @@
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pf41n-v000319</t>
+          <t>makinsan-l4-pa066041</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -1650,12 +1650,11 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
-Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
-Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
-При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
+          <t>Полуприцеп-контейнеровоз Makinsan, универсальная платформа, 4 оси, 2023 год, в работе, полностью исправен.
+Оси SAF Intradisc 4×9 т с дисковыми тормозами — меньше износ и увереннее торможение в грузу. Пневматическая подвеска с подъёмом передней и задней оси — экономит резину и упрощает манёвры на порожняке. Тормозная система Wabco EBS 2S/2M со стояночным тормозом от энергоаккумуляторов, два противооткатных упора в комплекте.
+Шасси сварное, сталь ST52-3, изготовлено на роботизированном оборудовании — жёсткая рама под тяжёлые контейнерные перевозки. Опорный домкрат ОMS двухскоростной, 24 т. Электрика Aspock 24V по ECE R48, светодиодные фонари, два 7-контактных + один 15-контактный разъём.
+Грузоподъёмность 32 000 кг, разрешённая нагрузка на оси 36 000 кг, нагрузка на шкворень 11 000 кг. Общая длина 12 470 мм, снаряжённая масса 5 900 кг.
+Шины 385/55R22.5, комплект 8 колёс на стальных дисках.</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1665,14 +1664,14 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>2150000</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/makinsan-l4-pa066041/08.jpg</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1702,19 +1701,15 @@
       <c r="AA7" s="1" t="inlineStr"/>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>2150000</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD7" s="1" t="inlineStr">
-        <is>
-          <t>325000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD7" s="1" t="inlineStr"/>
       <c r="AE7" s="1" t="inlineStr"/>
       <c r="AF7" s="1" t="inlineStr"/>
       <c r="AG7" s="1" t="inlineStr"/>
@@ -1725,7 +1720,7 @@
       <c r="AL7" s="1" t="inlineStr"/>
       <c r="AM7" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN7" s="1" t="inlineStr"/>
@@ -1736,12 +1731,12 @@
       </c>
       <c r="AP7" s="1" t="inlineStr">
         <is>
-          <t>Steelbear</t>
+          <t>Makinsan</t>
         </is>
       </c>
       <c r="AQ7" s="1" t="inlineStr">
         <is>
-          <t>PF-41N</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="AR7" s="1" t="inlineStr">
@@ -1756,10 +1751,14 @@
       </c>
       <c r="AT7" s="1" t="inlineStr"/>
       <c r="AU7" s="1" t="inlineStr"/>
-      <c r="AV7" s="1" t="inlineStr"/>
+      <c r="AV7" s="1" t="inlineStr">
+        <is>
+          <t>NP9L4CCP0PA066041</t>
+        </is>
+      </c>
       <c r="AW7" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX7" s="1" t="inlineStr">
@@ -1779,12 +1778,12 @@
       </c>
       <c r="BA7" s="1" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="BB7" s="1" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="BC7" s="1" t="inlineStr"/>
@@ -1801,7 +1800,7 @@
       <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-avg36</t>
+          <t>steelbear-pf41n-v000319</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -1818,13 +1817,12 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L Fox), 3-х осный, под заказ.
-Осевой агрегат Fox, барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
-6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
-Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
+          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
+Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
+Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
 При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
+Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1834,14 +1832,14 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>2960000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1871,7 +1869,7 @@
       <c r="AA8" s="1" t="inlineStr"/>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>2960000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1881,7 +1879,7 @@
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>296000</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr"/>
@@ -1910,7 +1908,7 @@
       </c>
       <c r="AQ8" s="1" t="inlineStr">
         <is>
-          <t>PL-24L</t>
+          <t>PF-41N</t>
         </is>
       </c>
       <c r="AR8" s="1" t="inlineStr">
@@ -1920,7 +1918,7 @@
       </c>
       <c r="AS8" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT8" s="1" t="inlineStr"/>
@@ -1933,7 +1931,7 @@
       </c>
       <c r="AX8" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY8" s="1" t="inlineStr">
@@ -1943,17 +1941,17 @@
       </c>
       <c r="AZ8" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA8" s="1" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="BB8" s="1" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="BC8" s="1" t="inlineStr"/>
@@ -1970,7 +1968,7 @@
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>steelbear-pl24l-avg36</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -1987,13 +1985,13 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
-Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L Fox), 3-х осный, под заказ.
+Осевой агрегат Fox, барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
+6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
+Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
+При покупке в лизинг — скидка от Минпромторга 10%.
+Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -2003,14 +2001,14 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2040,7 +2038,7 @@
       <c r="AA9" s="1" t="inlineStr"/>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
@@ -2048,7 +2046,11 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD9" s="1" t="inlineStr"/>
+      <c r="AD9" s="1" t="inlineStr">
+        <is>
+          <t>296000</t>
+        </is>
+      </c>
       <c r="AE9" s="1" t="inlineStr"/>
       <c r="AF9" s="1" t="inlineStr"/>
       <c r="AG9" s="1" t="inlineStr"/>
@@ -2059,7 +2061,7 @@
       <c r="AL9" s="1" t="inlineStr"/>
       <c r="AM9" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN9" s="1" t="inlineStr"/>
@@ -2090,14 +2092,10 @@
       </c>
       <c r="AT9" s="1" t="inlineStr"/>
       <c r="AU9" s="1" t="inlineStr"/>
-      <c r="AV9" s="1" t="inlineStr">
-        <is>
-          <t>XWZ9412LLR1202021</t>
-        </is>
-      </c>
+      <c r="AV9" s="1" t="inlineStr"/>
       <c r="AW9" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX9" s="1" t="inlineStr">
@@ -2117,7 +2115,7 @@
       </c>
       <c r="BA9" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="BB9" s="1" t="inlineStr">
@@ -2139,7 +2137,7 @@
       <c r="C10" s="1" t="inlineStr"/>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>tonar-b313-9888</t>
+          <t>steelbear-pl24l-ea653666</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -2156,12 +2154,13 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
-Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
-Итоговая цена при лизинге: 2 520 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
+Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -2171,14 +2170,14 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2208,7 +2207,7 @@
       <c r="AA10" s="1" t="inlineStr"/>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
@@ -2216,17 +2215,9 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD10" s="1" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
-      </c>
+      <c r="AD10" s="1" t="inlineStr"/>
       <c r="AE10" s="1" t="inlineStr"/>
-      <c r="AF10" s="1" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
-      </c>
+      <c r="AF10" s="1" t="inlineStr"/>
       <c r="AG10" s="1" t="inlineStr"/>
       <c r="AH10" s="1" t="inlineStr"/>
       <c r="AI10" s="1" t="inlineStr"/>
@@ -2235,7 +2226,7 @@
       <c r="AL10" s="1" t="inlineStr"/>
       <c r="AM10" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN10" s="1" t="inlineStr"/>
@@ -2246,12 +2237,12 @@
       </c>
       <c r="AP10" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>Steelbear</t>
         </is>
       </c>
       <c r="AQ10" s="1" t="inlineStr">
         <is>
-          <t>B3-13 (9888)</t>
+          <t>PL-24L</t>
         </is>
       </c>
       <c r="AR10" s="1" t="inlineStr">
@@ -2261,15 +2252,19 @@
       </c>
       <c r="AS10" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT10" s="1" t="inlineStr"/>
       <c r="AU10" s="1" t="inlineStr"/>
-      <c r="AV10" s="1" t="inlineStr"/>
+      <c r="AV10" s="1" t="inlineStr">
+        <is>
+          <t>XWZ9412LLR1202021</t>
+        </is>
+      </c>
       <c r="AW10" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX10" s="1" t="inlineStr">
@@ -2289,12 +2284,12 @@
       </c>
       <c r="BA10" s="1" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="BB10" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="BC10" s="1" t="inlineStr"/>
@@ -2311,7 +2306,7 @@
       <c r="C11" s="1" t="inlineStr"/>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-99891-order</t>
+          <t>tonar-b313-9888</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -2328,13 +2323,12 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
-(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
+          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
+Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
+Итоговая цена при лизинге: 2 520 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -2344,14 +2338,14 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr"/>
@@ -2381,7 +2375,7 @@
       <c r="AA11" s="1" t="inlineStr"/>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -2391,13 +2385,13 @@
       </c>
       <c r="AD11" s="1" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="AE11" s="1" t="inlineStr"/>
       <c r="AF11" s="1" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="AG11" s="1" t="inlineStr"/>
@@ -2424,7 +2418,7 @@
       </c>
       <c r="AQ11" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99891)</t>
+          <t>B3-13 (9888)</t>
         </is>
       </c>
       <c r="AR11" s="1" t="inlineStr">
@@ -2434,7 +2428,7 @@
       </c>
       <c r="AS11" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Бортовой</t>
         </is>
       </c>
       <c r="AT11" s="1" t="inlineStr"/>
@@ -2447,7 +2441,7 @@
       </c>
       <c r="AX11" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY11" s="1" t="inlineStr">
@@ -2462,12 +2456,12 @@
       </c>
       <c r="BA11" s="1" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="BB11" s="1" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC11" s="1" t="inlineStr"/>
@@ -2484,7 +2478,7 @@
       <c r="C12" s="1" t="inlineStr"/>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-p0002033</t>
+          <t>tonar-k4u-99891-order</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -2501,10 +2495,13 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
+(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2514,14 +2511,14 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
         </is>
       </c>
       <c r="S12" s="1" t="inlineStr"/>
@@ -2551,7 +2548,7 @@
       <c r="AA12" s="1" t="inlineStr"/>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC12" s="1" t="inlineStr">
@@ -2559,9 +2556,17 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD12" s="1" t="inlineStr"/>
+      <c r="AD12" s="1" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
       <c r="AE12" s="1" t="inlineStr"/>
-      <c r="AF12" s="1" t="inlineStr"/>
+      <c r="AF12" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
       <c r="AG12" s="1" t="inlineStr"/>
       <c r="AH12" s="1" t="inlineStr"/>
       <c r="AI12" s="1" t="inlineStr"/>
@@ -2570,7 +2575,7 @@
       <c r="AL12" s="1" t="inlineStr"/>
       <c r="AM12" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN12" s="1" t="inlineStr"/>
@@ -2601,14 +2606,10 @@
       </c>
       <c r="AT12" s="1" t="inlineStr"/>
       <c r="AU12" s="1" t="inlineStr"/>
-      <c r="AV12" s="1" t="inlineStr">
-        <is>
-          <t>X0T998910P0002033</t>
-        </is>
-      </c>
+      <c r="AV12" s="1" t="inlineStr"/>
       <c r="AW12" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX12" s="1" t="inlineStr">
@@ -2618,12 +2619,12 @@
       </c>
       <c r="AY12" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ12" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA12" s="1" t="inlineStr">
@@ -2633,7 +2634,7 @@
       </c>
       <c r="BB12" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="BC12" s="1" t="inlineStr"/>
@@ -2650,7 +2651,7 @@
       <c r="C13" s="1" t="inlineStr"/>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>tonar-l3-9445</t>
+          <t>tonar-k4u-p0002033</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
@@ -2667,12 +2668,10 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2682,14 +2681,14 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
       <c r="S13" s="1" t="inlineStr"/>
@@ -2719,7 +2718,7 @@
       <c r="AA13" s="1" t="inlineStr"/>
       <c r="AB13" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
@@ -2727,17 +2726,9 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>320000</t>
-        </is>
-      </c>
+      <c r="AD13" s="1" t="inlineStr"/>
       <c r="AE13" s="1" t="inlineStr"/>
-      <c r="AF13" s="1" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
+      <c r="AF13" s="1" t="inlineStr"/>
       <c r="AG13" s="1" t="inlineStr"/>
       <c r="AH13" s="1" t="inlineStr"/>
       <c r="AI13" s="1" t="inlineStr"/>
@@ -2746,7 +2737,7 @@
       <c r="AL13" s="1" t="inlineStr"/>
       <c r="AM13" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN13" s="1" t="inlineStr"/>
@@ -2762,7 +2753,7 @@
       </c>
       <c r="AQ13" s="1" t="inlineStr">
         <is>
-          <t>L3 (9445)</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR13" s="1" t="inlineStr">
@@ -2772,47 +2763,47 @@
       </c>
       <c r="AS13" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT13" s="1" t="inlineStr"/>
       <c r="AU13" s="1" t="inlineStr"/>
-      <c r="AV13" s="1" t="inlineStr"/>
+      <c r="AV13" s="1" t="inlineStr">
+        <is>
+          <t>X0T998910P0002033</t>
+        </is>
+      </c>
       <c r="AW13" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX13" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY13" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ13" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA13" s="1" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="BB13" s="1" t="inlineStr">
         <is>
-          <t>12800</t>
-        </is>
-      </c>
-      <c r="BC13" s="1" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC13" s="1" t="inlineStr"/>
       <c r="BD13" s="1" t="inlineStr"/>
       <c r="BE13" s="1" t="inlineStr"/>
     </row>
@@ -2826,7 +2817,7 @@
       <c r="C14" s="1" t="inlineStr"/>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>tonar-reef-r313</t>
+          <t>tonar-l3-9445</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
@@ -2843,11 +2834,11 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
-В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
-Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 6 865 000 ₽.
+          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -2858,14 +2849,14 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr"/>
@@ -2895,7 +2886,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
@@ -2905,11 +2896,15 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr"/>
-      <c r="AF14" s="1" t="inlineStr"/>
+      <c r="AF14" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
       <c r="AG14" s="1" t="inlineStr"/>
       <c r="AH14" s="1" t="inlineStr"/>
       <c r="AI14" s="1" t="inlineStr"/>
@@ -2934,7 +2929,7 @@
       </c>
       <c r="AQ14" s="1" t="inlineStr">
         <is>
-          <t>R3-13</t>
+          <t>L3 (9445)</t>
         </is>
       </c>
       <c r="AR14" s="1" t="inlineStr">
@@ -2944,7 +2939,7 @@
       </c>
       <c r="AS14" s="1" t="inlineStr">
         <is>
-          <t>Рефрижератор</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT14" s="1" t="inlineStr"/>
@@ -2967,22 +2962,22 @@
       </c>
       <c r="AZ14" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA14" s="1" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="BB14" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="BC14" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BD14" s="1" t="inlineStr"/>
@@ -2998,7 +2993,7 @@
       <c r="C15" s="1" t="inlineStr"/>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>tonar-samosval-9595</t>
+          <t>tonar-reef-r313</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -3015,10 +3010,11 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
-Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
-Итоговая цена при лизинге: 3 780 000 ₽.
+          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
+В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
+Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 6 865 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3029,14 +3025,14 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>4200000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg</t>
         </is>
       </c>
       <c r="S15" s="1" t="inlineStr"/>
@@ -3066,7 +3062,7 @@
       <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>4200000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -3076,7 +3072,7 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
@@ -3105,7 +3101,7 @@
       </c>
       <c r="AQ15" s="1" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>R3-13</t>
         </is>
       </c>
       <c r="AR15" s="1" t="inlineStr">
@@ -3115,7 +3111,7 @@
       </c>
       <c r="AS15" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="AT15" s="1" t="inlineStr"/>
@@ -3128,7 +3124,7 @@
       </c>
       <c r="AX15" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY15" s="1" t="inlineStr">
@@ -3138,18 +3134,22 @@
       </c>
       <c r="AZ15" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA15" s="1" t="inlineStr">
         <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="BB15" s="1" t="inlineStr"/>
+          <t>31200</t>
+        </is>
+      </c>
+      <c r="BB15" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
       <c r="BC15" s="1" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BD15" s="1" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
       <c r="C16" s="1" t="inlineStr"/>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>tonar-sdp489-95895</t>
+          <t>tonar-samosval-9595</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
@@ -3182,11 +3182,10 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
-Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
-Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 7 150 000 ₽.
+          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
+Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
+Итоговая цена при лизинге: 3 780 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3197,14 +3196,14 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>7650000</t>
+          <t>4200000</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr"/>
@@ -3234,7 +3233,7 @@
       <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>7650000</t>
+          <t>4200000</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
@@ -3244,7 +3243,7 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>
@@ -3273,7 +3272,7 @@
       </c>
       <c r="AQ16" s="1" t="inlineStr">
         <is>
-          <t>SDP4-89 (95895)</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="AR16" s="1" t="inlineStr">
@@ -3283,7 +3282,7 @@
       </c>
       <c r="AS16" s="1" t="inlineStr">
         <is>
-          <t>Щеповоз</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AT16" s="1" t="inlineStr"/>
@@ -3306,22 +3305,18 @@
       </c>
       <c r="AZ16" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA16" s="1" t="inlineStr">
         <is>
-          <t>27800</t>
-        </is>
-      </c>
-      <c r="BB16" s="1" t="inlineStr">
-        <is>
-          <t>14600</t>
-        </is>
-      </c>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="BB16" s="1" t="inlineStr"/>
       <c r="BC16" s="1" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BD16" s="1" t="inlineStr"/>
@@ -3337,7 +3332,7 @@
       <c r="C17" s="1" t="inlineStr"/>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>tonar-t313-9888</t>
+          <t>tonar-sdp489-95895</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr"/>
@@ -3354,11 +3349,11 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
-Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
-Итоговая цена при лизинге: 3 040 000 ₽.
+          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
+Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
+Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 7 150 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3369,14 +3364,14 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>7650000</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
         </is>
       </c>
       <c r="S17" s="1" t="inlineStr"/>
@@ -3406,7 +3401,7 @@
       <c r="AA17" s="1" t="inlineStr"/>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>7650000</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
@@ -3416,15 +3411,11 @@
       </c>
       <c r="AD17" s="1" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE17" s="1" t="inlineStr"/>
-      <c r="AF17" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
+      <c r="AF17" s="1" t="inlineStr"/>
       <c r="AG17" s="1" t="inlineStr"/>
       <c r="AH17" s="1" t="inlineStr"/>
       <c r="AI17" s="1" t="inlineStr"/>
@@ -3449,7 +3440,7 @@
       </c>
       <c r="AQ17" s="1" t="inlineStr">
         <is>
-          <t>T3-13 (9888)</t>
+          <t>SDP4-89 (95895)</t>
         </is>
       </c>
       <c r="AR17" s="1" t="inlineStr">
@@ -3459,7 +3450,7 @@
       </c>
       <c r="AS17" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Щеповоз</t>
         </is>
       </c>
       <c r="AT17" s="1" t="inlineStr"/>
@@ -3472,7 +3463,7 @@
       </c>
       <c r="AX17" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY17" s="1" t="inlineStr">
@@ -3487,17 +3478,17 @@
       </c>
       <c r="BA17" s="1" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>27800</t>
         </is>
       </c>
       <c r="BB17" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="BC17" s="1" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD17" s="1" t="inlineStr"/>
@@ -3513,7 +3504,7 @@
       <c r="C18" s="1" t="inlineStr"/>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>tonar-zernovoz-95941</t>
+          <t>tonar-t313-9888</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
@@ -3530,10 +3521,11 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
-Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 4 900 000 ₽.
+          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
+Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
+Итоговая цена при лизинге: 3 040 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3544,14 +3536,14 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>3800000</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S18" s="1" t="inlineStr"/>
@@ -3581,7 +3573,7 @@
       <c r="AA18" s="1" t="inlineStr"/>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>3800000</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
@@ -3591,11 +3583,15 @@
       </c>
       <c r="AD18" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>380000</t>
         </is>
       </c>
       <c r="AE18" s="1" t="inlineStr"/>
-      <c r="AF18" s="1" t="inlineStr"/>
+      <c r="AF18" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
       <c r="AG18" s="1" t="inlineStr"/>
       <c r="AH18" s="1" t="inlineStr"/>
       <c r="AI18" s="1" t="inlineStr"/>
@@ -3620,7 +3616,7 @@
       </c>
       <c r="AQ18" s="1" t="inlineStr">
         <is>
-          <t>95941</t>
+          <t>T3-13 (9888)</t>
         </is>
       </c>
       <c r="AR18" s="1" t="inlineStr">
@@ -3630,7 +3626,7 @@
       </c>
       <c r="AS18" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AT18" s="1" t="inlineStr"/>
@@ -3653,7 +3649,7 @@
       </c>
       <c r="AZ18" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA18" s="1" t="inlineStr">
@@ -3661,10 +3657,14 @@
           <t>31000</t>
         </is>
       </c>
-      <c r="BB18" s="1" t="inlineStr"/>
+      <c r="BB18" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
       <c r="BC18" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD18" s="1" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
       <c r="C19" s="1" t="inlineStr"/>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tonar-zernovoz-95941</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
@@ -3697,10 +3697,11 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
+Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 4 900 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -3710,14 +3711,14 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr"/>
@@ -3747,7 +3748,7 @@
       <c r="AA19" s="1" t="inlineStr"/>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="AC19" s="1" t="inlineStr">
@@ -3755,7 +3756,11 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD19" s="1" t="inlineStr"/>
+      <c r="AD19" s="1" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
       <c r="AE19" s="1" t="inlineStr"/>
       <c r="AF19" s="1" t="inlineStr"/>
       <c r="AG19" s="1" t="inlineStr"/>
@@ -3766,7 +3771,7 @@
       <c r="AL19" s="1" t="inlineStr"/>
       <c r="AM19" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN19" s="1" t="inlineStr"/>
@@ -3777,12 +3782,12 @@
       </c>
       <c r="AP19" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ19" s="1" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>95941</t>
         </is>
       </c>
       <c r="AR19" s="1" t="inlineStr">
@@ -3792,19 +3797,15 @@
       </c>
       <c r="AS19" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AT19" s="1" t="inlineStr"/>
       <c r="AU19" s="1" t="inlineStr"/>
-      <c r="AV19" s="1" t="inlineStr">
-        <is>
-          <t>XZFVKRP3DR0000119</t>
-        </is>
-      </c>
+      <c r="AV19" s="1" t="inlineStr"/>
       <c r="AW19" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX19" s="1" t="inlineStr">
@@ -3819,26 +3820,192 @@
       </c>
       <c r="AZ19" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA19" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="BB19" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
+          <t>31000</t>
+        </is>
+      </c>
+      <c r="BB19" s="1" t="inlineStr"/>
       <c r="BC19" s="1" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>50</t>
         </is>
       </c>
       <c r="BD19" s="1" t="inlineStr"/>
       <c r="BE19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V20" s="1" t="inlineStr"/>
+      <c r="W20" s="1" t="inlineStr"/>
+      <c r="X20" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y20" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z20" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA20" s="1" t="inlineStr"/>
+      <c r="AB20" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC20" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD20" s="1" t="inlineStr"/>
+      <c r="AE20" s="1" t="inlineStr"/>
+      <c r="AF20" s="1" t="inlineStr"/>
+      <c r="AG20" s="1" t="inlineStr"/>
+      <c r="AH20" s="1" t="inlineStr"/>
+      <c r="AI20" s="1" t="inlineStr"/>
+      <c r="AJ20" s="1" t="inlineStr"/>
+      <c r="AK20" s="1" t="inlineStr"/>
+      <c r="AL20" s="1" t="inlineStr"/>
+      <c r="AM20" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN20" s="1" t="inlineStr"/>
+      <c r="AO20" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP20" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ20" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AR20" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS20" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT20" s="1" t="inlineStr"/>
+      <c r="AU20" s="1" t="inlineStr"/>
+      <c r="AV20" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW20" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX20" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY20" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ20" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA20" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB20" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC20" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD20" s="1" t="inlineStr"/>
+      <c r="BE20" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -959,7 +959,7 @@
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-контейнеровоз ИнтерПрицеп 853375, 2024 год, в работе, полностью исправен.
-4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины на порожняке и разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
+4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины без груза и на разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
 Берёт контейнеры 20', 30', 40' и High Cube — под большинство стандартных грузоперевозок без переоборудования. Разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг. Высота погрузки 1 100 мм.
 Инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
@@ -1651,7 +1651,7 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-контейнеровоз Makinsan, универсальная платформа, 4 оси, 2023 год, в работе, полностью исправен.
-Оси SAF Intradisc 4×9 т с дисковыми тормозами — меньше износ и увереннее торможение в грузу. Пневматическая подвеска с подъёмом передней и задней оси — экономит резину и упрощает манёвры на порожняке. Тормозная система Wabco EBS 2S/2M со стояночным тормозом от энергоаккумуляторов, два противооткатных упора в комплекте.
+Оси SAF Intradisc 4×9 т с дисковыми тормозами — меньше износ и увереннее торможение под нагрузкой. Пневматическая подвеска с подъёмом передней и задней оси — экономит резину и упрощает манёвры без груза. Тормозная система Wabco EBS 2S/2M со стояночным тормозом от энергоаккумуляторов, два противооткатных упора в комплекте.
 Шасси сварное, сталь ST52-3, изготовлено на роботизированном оборудовании — жёсткая рама под тяжёлые контейнерные перевозки. Опорный домкрат ОMS двухскоростной, 24 т. Электрика Aspock 24V по ECE R48, светодиодные фонари, два 7-контактных + один 15-контактный разъём.
 Грузоподъёмность 32 000 кг, разрешённая нагрузка на оси 36 000 кг, нагрузка на шкворень 11 000 кг. Общая длина 12 470 мм, снаряжённая масса 5 900 кг.
 Шины 385/55R22.5, комплект 8 колёс на стальных дисках.</t>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины без груза. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
 Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
 Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
 При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
@@ -2834,7 +2834,7 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
+          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ без груза. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
 Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
 Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
 При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
@@ -3865,7 +3865,7 @@
       <c r="M20" s="1" t="inlineStr">
         <is>
           <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+Оси SAF, подъёмная передняя — меньше износ резины и расход без груза. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
 13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2155,7 +2155,7 @@
       <c r="M10" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
-Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, дисковые тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
 6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
 Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AZ10" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA10" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -892,10 +892,14 @@
       </c>
       <c r="AT2" s="1" t="inlineStr"/>
       <c r="AU2" s="1" t="inlineStr"/>
-      <c r="AV2" s="1" t="inlineStr"/>
+      <c r="AV2" s="1" t="inlineStr">
+        <is>
+          <t>EAR853372R0000830</t>
+        </is>
+      </c>
       <c r="AW2" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX2" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="AC2" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD2" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -782,7 +782,11 @@
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -954,7 +958,11 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1121,7 +1129,11 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1296,7 +1308,11 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1471,7 +1487,11 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1646,7 +1666,11 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1813,7 +1837,11 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1981,7 +2009,11 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2150,7 +2182,11 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2319,7 +2355,11 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2491,7 +2531,11 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2664,7 +2708,11 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2830,7 +2878,11 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3006,7 +3058,11 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3178,7 +3234,11 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3345,7 +3405,11 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3517,7 +3581,11 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3693,7 +3761,11 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3860,7 +3932,11 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -418,8 +418,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -769,8 +769,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>interpricep-853372-halfpipe</t>
@@ -945,8 +953,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>interpricep-853375-r0000773</t>
@@ -1116,8 +1132,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
           <t>kassbohrer-maxima-shtor-00116344</t>
@@ -1295,8 +1319,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
           <t>kassbohrer-maxima-shtor-00124397</t>
@@ -1474,8 +1506,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
           <t>kassbohrer-maxima-shtor-00124732</t>
@@ -1653,8 +1693,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>makinsan-l4-pa066041</t>
@@ -1824,8 +1872,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
           <t>steelbear-pf41n-v000319</t>
@@ -1996,8 +2052,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
           <t>steelbear-pl24l-avg36</t>
@@ -2169,8 +2233,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
           <t>steelbear-pl24l-ea653666</t>
@@ -2342,8 +2414,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
           <t>tonar-b313-9888</t>
@@ -2518,8 +2598,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-99891-order</t>
@@ -2695,8 +2783,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-p0002033</t>
@@ -2865,8 +2961,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
           <t>tonar-l3-9445</t>
@@ -3045,8 +3149,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
           <t>tonar-reef-r313</t>
@@ -3221,8 +3333,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
           <t>tonar-samosval-9595</t>
@@ -3377,7 +3497,11 @@
           <t>30000</t>
         </is>
       </c>
-      <c r="BB16" s="1" t="inlineStr"/>
+      <c r="BB16" s="1" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
       <c r="BC16" s="1" t="inlineStr">
         <is>
           <t>33.6</t>
@@ -3392,8 +3516,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
           <t>tonar-sdp489-95895</t>
@@ -3568,8 +3700,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
           <t>tonar-t313-9888</t>
@@ -3748,8 +3888,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
           <t>tonar-zernovoz-95941</t>
@@ -3904,7 +4052,11 @@
           <t>31000</t>
         </is>
       </c>
-      <c r="BB19" s="1" t="inlineStr"/>
+      <c r="BB19" s="1" t="inlineStr">
+        <is>
+          <t>12166</t>
+        </is>
+      </c>
       <c r="BC19" s="1" t="inlineStr">
         <is>
           <t>50</t>
@@ -3919,8 +4071,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
           <t>v-trailer-329d-r0000119</t>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3104,7 +3104,8 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии, ЭПТС оформлен — можно забрать сразу.
+          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
+Цена снижена: в объявлении она указана уже со скидкой.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
 Гарантия завода — 3 года.
@@ -3120,7 +3121,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>3040000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -3157,7 +3158,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>3040000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
@@ -3167,7 +3168,7 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>289000</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr"/>
@@ -3297,7 +3298,8 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии, ЭПТС оформлен — можно забрать сразу.
+          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
+Цена снижена: в объявлении она указана уже со скидкой.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
 Гарантия завода — 3 года.
@@ -3313,7 +3315,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>3040000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -3350,7 +3352,7 @@
       <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>3040000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -3360,7 +3362,7 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>289000</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
@@ -3490,7 +3492,8 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии, ЭПТС оформлен — можно забрать сразу.
+          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
+Цена снижена: в объявлении она указана уже со скидкой.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
 Гарантия завода — 3 года.
@@ -3506,7 +3509,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>3040000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -3543,7 +3546,7 @@
       <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>3040000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
@@ -3553,7 +3556,7 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>289000</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3121,7 +3121,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>2980000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -3158,7 +3158,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>2980000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>289000</t>
+          <t>298000</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr"/>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>2980000</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>2980000</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>289000</t>
+          <t>298000</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>2980000</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
       <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>2980000</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>289000</t>
+          <t>298000</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3105,7 +3105,7 @@
       <c r="M14" s="1" t="inlineStr">
         <is>
           <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
-Цена снижена: в объявлении она указана уже со скидкой.
+Действует скидка — уточняйте у менеджера.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
 Гарантия завода — 3 года.
@@ -3121,7 +3121,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
+          <t>3040000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -3158,7 +3158,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
+          <t>3040000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>298000</t>
+          <t>364000</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
-Цена снижена: в объявлении она указана уже со скидкой.
+Действует скидка — уточняйте у менеджера.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
 Гарантия завода — 3 года.
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
+          <t>3040000</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
+          <t>3040000</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>298000</t>
+          <t>364000</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
@@ -3493,7 +3493,7 @@
       <c r="M16" s="1" t="inlineStr">
         <is>
           <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
-Цена снижена: в объявлении она указана уже со скидкой.
+Действует скидка — уточняйте у менеджера.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
 Гарантия завода — 3 года.
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
+          <t>3040000</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
       <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
+          <t>3040000</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>298000</t>
+          <t>364000</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -417,7 +417,7 @@
   <dimension ref="A1:BE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
@@ -437,7 +437,7 @@
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="31" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
@@ -1709,7 +1709,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15с2</t>
+          <t>Ставропольский край, с. Надежда, ул. Ставропольская, 83</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
@@ -1774,7 +1774,7 @@
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15с2</t>
+          <t>Ставропольский край, с. Надежда, ул. Ставропольская, 83</t>
         </is>
       </c>
       <c r="V7" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -810,7 +810,7 @@
 Гарантия 24 месяца без ограничения пробега. Комплектующие — BPW, JOST, Ermax, Binotto, Camozzi, AKKAR.
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -1933,7 +1933,7 @@
 Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -2491,10 +2491,8 @@
       <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины без груза. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
-Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
-Итоговая цена при лизинге: 2 520 000 ₽.
+Скидка от производителя на линейку бортовых прицепов — 10%.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Характеристики:
 - Борт: Алюминий
@@ -2705,10 +2703,8 @@
       <c r="M12" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
+Скидка от производителя на линейку контейнеровозов — 5%.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 (У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)
 Характеристики:
@@ -2738,7 +2734,7 @@
 - Опорное устройство: на 24 т
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -3111,7 +3107,7 @@
 Гарантия завода — 3 года.
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
@@ -3305,7 +3301,7 @@
 Гарантия завода — 3 года.
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
@@ -3499,7 +3495,7 @@
 Гарантия завода — 3 года.
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
@@ -3687,10 +3683,8 @@
       <c r="M17" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ без груза. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
+Скидка от производителя на линейку лесовозов — 5%.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Характеристики:
 - Количество осей: 3, 1-я подъемная
@@ -3717,7 +3711,7 @@
 - Подъёмная ось: передняя
 - Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
 ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Перений щит: стальной, с усилителями
+- Передний щит: стальной, с усилителями
 - Опорное устройство: на 24 т
 - Геометрический объём перевозимого груза, куб.м: 63
 - Коники: разборные
@@ -3914,16 +3908,14 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
-В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
-Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 6 865 000 ₽.
+          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 86,9 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
+В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины.
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Характеристики:
 - Количество осей: 3
 - Кузов: сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну.
-- Объем: 87 куб.м.
+- Объём: 86,9 куб.м
 - Подвеска: рычажного типа
 - ССУ: 1150
 - Тип: рефрижераторный полуприцеп
@@ -3937,18 +3929,18 @@
 ВЕС:
 - Масса снаряженного полуприцепа, не более, кг: 8 600
 - Разрешенная максимальная масса, кг: 38 080
-- Нагрузка на колесную тележку, кг: 10 870
-- Нагрузка на ССУ, кг: 27 000
+- Нагрузка на колёсную тележку, кг: 27 000
+- Нагрузка на ССУ, кг: 10 870
 ОСИ:
 - Оси колес: Тонар
 - Шины: бескамерные 385/65 R22.5
 - Подъемные оси: 1-ая (базовая комплектация)
 - Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
 ПРЕИМУЩЕСТВА:
-- Мы разработали облегченную раму из высокопрочной стали, которая сочетает надежность и ремонтопригодность благодаря модульной конструкции: в случае повреждения достаточно заменить только неисправную секцию.
+- Облегчённая рама из высокопрочной стали, модульная: при повреждении меняется только неисправная секция.
 - Цинкование рамы защищает ее от влаги, реагентов и соли, гарантируя исключительную долговечность, даже в суровых условиях.
 ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Объем кузова, куб.м: 87
+- Объём кузова, куб.м: 86,9
 - Количество европалет, шт: 33
 - Задняя стенка: двустворчатая дверь, каждая створка на 3-х петлях; двойные поворотные штанговые запоры; 3-х уровневый резиновый уплотнитель; рама заднего проема из нержавеющей стали
 - Боковые стенки: сэндвич-панели с усиленной жесткостью
@@ -3957,7 +3949,7 @@
 - Крыша: сэндвич-панели; 6 потолочных светодиодных фонарей внутреннего освещения обеспечивают высокую яркость и низкое энергопотребление
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
@@ -4145,9 +4137,7 @@
       <c r="M19" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
-Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
-Итоговая цена при лизинге: 3 780 000 ₽.
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Характеристики:
 - Количество осей: 4
@@ -4175,7 +4165,6 @@
 - Оси колес: Тонар
 - Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
 ПРЕИМУЩЕСТВА:
-- Предназначен для перевозки зерновых культур.
 - Снаряженная масса 7 900 кг.
 - Габаритная высота не превышает 3,2 метра (!).
 ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
@@ -4188,7 +4177,7 @@
 - Минимальный объем масляного бака тягача, л: 150
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -4377,9 +4366,7 @@
         <is>
           <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
 Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
-Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 7 150 000 ₽.
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
@@ -4571,10 +4558,8 @@
       <c r="M21" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
-Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
-Итоговая цена при лизинге: 3 040 000 ₽.
+Скидка от производителя на линейку шторных прицепов — 10%.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Характеристики:
 - Количество осей: 3
@@ -4806,49 +4791,44 @@
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
-Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 4 900 000 ₽.
+          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый прямоугольный кузов, объём 50 м³, до 33,2 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными лючками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
 Гарантия завода — 3 года. Поставка после согласования комплектации.
 Характеристики:
-- Количество осей: 4, 1-я подъемная
-- Кузов: прямоугольным кузов, комбинированный задний борт (откидной и распашной) дополнительно оснащен разгрузочными лючками; с возможностью боковой разгрузки
-- Объем: 41 / 48 куб.м.
+- Количество осей: 3, 1-я подъёмная
+- Кузов: алюминиевый прямоугольный; комбинированный задний борт (откидной и распашной) с разгрузочными лючками
+- Объём кузова: 50 куб.м
 - Подвеска: рычажного типа
-- ССУ: 1200 / 1350
+- ССУ: 1200
 - Тент: с механическим приводом, входит в базовую комплектацию
 - Тип: самосвальный полуприцеп-зерновоз
 - Тип ошиновки: односкатная
 - Тормозная система: TEBS
 - Дополнительные опции: установка надставных бортов
 РАЗМЕРЫ:
-- Длина кузова, мм: 9834
-- Ширина кузова, мм: 2550
-- Высота, мм: 3400
-- Высота седельно-сцепного устройства, мм: 1200
+- Длина кузова, мм: 12 166
+- Ширина кузова, мм: 2 550
+- Высота, мм: 3 621
+- Высота седельно-сцепного устройства, мм: 1 200
 ВЕС:
-- Масса снаряженного полуприцепа, не более, кг: 6880
-- Масса перевозимого груза, кг: 31000
-- Нагрузка на ССУ, кг: 11000
-- Осевая нагрузка, кг: 27000
+- Масса снаряженного полуприцепа, не более, кг: 7 600
+- Масса перевозимого груза, кг: 33 200
+- Нагрузка на ССУ, кг: 14 000
+- Осевая нагрузка, кг: 27 000
 ОСИ:
 - Оси колёс: Тонар
 - Шины: бескамерные 385/65R 22,5
 - Подъёмная ось: передняя
 - Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
 ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Задний борт: комбинированный, откидной и распашной, дополнительно оснащен разгрузочными лючками
-- Боковые борта: выполнены из алюминиевого профиля; с разгрузочными лючками по правой стороне
-- Тент: с механическим приводом, входит в базовую комплектацию
-- Объём кузова, куб.м: 41 / 48
+- Боковые борта: из алюминиевого профиля
 - Колея колёс, мм: 2 040
 - Опорное устройство: на 24 т
 - Угол подъёма кузова, град: 45
 - Минимальный объём масляного бака тягача, л: 150
 Доставка по России.
 Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
@@ -4980,7 +4960,7 @@
       </c>
       <c r="BA22" s="1" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="BB22" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -802,15 +802,28 @@
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-самосвал с задним свалом ИнтерПрицеп 853372 «Халф Пайп», 4-осный, в наличии.
-Пневмоподвеска с механизмом подъёма на первой-второй осях. Оси барабанные, 12 тонн, L1 (Китай), гидроцилиндр Atlant (Россия). Тормозная система ABS SORL (аналог WABCO). Шины 385/65R22,5 Tyrex, комплект 8+1 запасное.
-Кузов графитово-серый/чёрный, лакокрасочное покрытие двухслойное, рама — антигравийное покрытие. Толщина стенок кузова 5 мм, пола 6 мм. Задний борт с клапаном. Полог со сматывающим устройством.
-Грузоподъёмность 37 000 кг, снаряжённая масса 10 000 кг, максимальная масса 47 000 кг. Нагрузка на оси 32 000 кг, на седло 15 000 кг. Внутренние размеры кузова 10 200×2 330×2 000 мм, объём кузова 44 м³. Погрузочная высота 1 450 мм, высота седельно-сцепного устройства 1 150–1 250 мм.
-Инструментальный ящик Daken, рукомойник Lokhen (Италия), 2 корзины запасного колеса.
-Гарантия 24 месяца без ограничения пробега. Комплектующие — BPW, JOST, Ermax, Binotto, Camozzi, AKKAR.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-самосвал с задним свалом ИнтерПрицеп 853372 «Халф Пайп», новый, 2024 года, в наличии. 4 оси, кузов 44 м³.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— гарантия 24 месяца без ограничения пробега;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— оси барабанные, 12 т, L1 (Китай); пневмоподвеска с подъёмом 1-й и 2-й осей;
+— тормозная система ABS SORL (аналог WABCO);
+— гидроцилиндр Atlant (Россия);
+— шины 385/65R22,5 Tyrex, 8 + 1 запасное;
+— кузов: стенки 5 мм, пол 6 мм, задний борт с клапаном, полог со сматывающим устройством;
+— покрытие кузова двухслойное, рамы — антигравийное; цвет графитово-серый/чёрный;
+— внутренние размеры кузова 10 200 × 2 330 × 2 000 мм, объём 44 м³;
+— грузоподъёмность 37 000 кг, снаряжённая масса 10 000 кг, максимальная 47 000 кг;
+— нагрузка на оси 32 000 кг, на седло 15 000 кг;
+— погрузочная высота 1 450 мм, высота ССУ 1 150–1 250 мм;
+— комплектующие BPW, JOST, Ermax, Binotto, Camozzi, AKKAR;
+— инструментальный ящик Daken, рукомойник Lokhen (Италия), 2 корзины запасного колеса.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -1001,12 +1014,21 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз ИнтерПрицеп 853375, 2024 год, в работе, полностью исправен.
-4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины без груза и на разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
-Берёт контейнеры 20', 30', 40' и High Cube — под большинство стандартных грузоперевозок без переоборудования. Разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг. Высота погрузки 1 100 мм.
-Инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп-контейнеровоз ИнтерПрицеп 853375, 2024 года, б/у. В работе, полностью исправен.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— возможна аренда с правом выкупа;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами.
+Технические характеристики
+— оси: 4 (3 + выносная балансирная), с подъёмом осей;
+— подвеска пневматическая; тормоза дисковые, ABS SORL;
+— шины 385/55R22.5, 8 + 1 запасное;
+— контейнеры 20', 30', 40' и High Cube;
+— разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг;
+— высота погрузки 1 100 мм;
+— инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
@@ -1181,16 +1203,21 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
-Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 года, б/у, TIR-исполнение. На ходу, полностью исправен, не требует вложений и ремонта.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— возможна аренда с правом выкупа;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами;
+— торг при осмотре.
+Технические характеристики
+— оси BPW, 3 шт.; подвеска зависимая, на продольных рычагах; тормоза дисковые;
+— шины бескамерные 385/65R22,5, односкат, Bridgestone;
+— снаряжённая масса 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная 37 500 кг;
+— внутренние размеры 16 520 × 2 480 × 2 700 мм, объём кузова 110,6 м³;
+— высота ССУ 1 150 мм;
+— боковая обшивка — фанера, пол — ламинированная фанера 27 мм.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr">
@@ -1369,16 +1396,21 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
-Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 года, б/у, TIR-исполнение. На ходу, полностью исправен, не требует вложений и ремонта.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— возможна аренда с правом выкупа;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами;
+— торг при осмотре.
+Технические характеристики
+— оси BPW, 3 шт.; подвеска зависимая, на продольных рычагах; тормоза дисковые;
+— шины бескамерные 385/65R22,5, односкат, Bridgestone;
+— снаряжённая масса 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная 37 500 кг;
+— внутренние размеры 16 520 × 2 480 × 2 700 мм, объём кузова 110,6 м³;
+— высота ССУ 1 150 мм;
+— боковая обшивка — фанера, пол — ламинированная фанера 27 мм.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
@@ -1557,16 +1589,21 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
-Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп шторный Kassbohrer, 2023 года, б/у, TIR-исполнение. На ходу, полностью исправен, не требует вложений и ремонта.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— возможна аренда с правом выкупа;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами;
+— торг при осмотре.
+Технические характеристики
+— оси BPW, 3 шт.; подвеска рессорная; тормоза барабанные;
+— шины бескамерные 385/65R22,5, односкат, Bridgestone;
+— снаряжённая масса 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная 39 000 кг;
+— внутренние размеры 13 600 × 2 480 × 2 700 мм, объём кузова 92 м³;
+— высота ССУ 1 150 мм;
+— боковая обшивка — фанера, пол — ламинированная фанера 30 мм.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
@@ -1745,12 +1782,22 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Makinsan, универсальная платформа, 4 оси, 2023 год, в работе, полностью исправен.
-Оси SAF Intradisc 4×9 т с дисковыми тормозами — меньше износ и увереннее торможение под нагрузкой. Пневматическая подвеска с подъёмом передней и задней оси — экономит резину и упрощает манёвры без груза. Тормозная система Wabco EBS 2S/2M со стояночным тормозом от энергоаккумуляторов, два противооткатных упора в комплекте.
-Шасси сварное, сталь ST52-3, изготовлено на роботизированном оборудовании — жёсткая рама под тяжёлые контейнерные перевозки. Опорный домкрат ОMS двухскоростной, 24 т. Электрика Aspock 24V по ECE R48, светодиодные фонари, два 7-контактных + один 15-контактный разъём.
-Грузоподъёмность 32 000 кг, разрешённая нагрузка на оси 36 000 кг, нагрузка на шкворень 11 000 кг. Общая длина 12 470 мм, снаряжённая масса 5 900 кг.
-Шины 385/55R22.5, комплект 8 колёс на стальных дисках.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп-контейнеровоз Makinsan L4, универсальная платформа, 2023 года, б/у. В работе, полностью исправен.
+Осмотр: Ставропольский край, с. Надежда, ул. Ставропольская, 83.
+Условия
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами.
+Технические характеристики
+— оси SAF Intradisc 4 × 9 т, дисковые тормоза;
+— пневмоподвеска с подъёмом передней и задней оси;
+— тормозная система Wabco EBS 2S/2M, стояночный тормоз от энергоаккумуляторов, 2 противооткатных упора;
+— шасси сварное, сталь ST52-3, роботизированная сварка;
+— опорный домкрат OMS двухскоростной, 24 т;
+— электрика Aspock 24V (ECE R48), светодиодные фонари, два 7-контактных и один 15-контактный разъём;
+— грузоподъёмность 32 000 кг, нагрузка на оси 36 000 кг, на шкворень 11 000 кг;
+— длина 12 470 мм, снаряжённая масса 5 900 кг;
+— шины 385/55R22.5, 8 колёс на стальных дисках.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1925,15 +1972,25 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
-Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
-Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
-При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (PF-41N FOX INTRA DISK), новый, под заказ. 4 оси, универсал.
+Поставка — 10 рабочих дней с момента предоплаты.
+Условия
+— заводская гарантия 12 месяцев;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— контейнеры: 1 × 40' (в т. ч. HQ), 2 × 20' или 1 × 20' по центру;
+— максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм;
+— осевой агрегат FOX B9-22S, дисковые тормоза, нагрузка на ось 9 000 кг;
+— усиленная пневмоподвеска FOX INTRA, подъём 1-й оси (ручной) и 2-й (автоматический);
+— тормозная система Haldex EBS 4S/2M с противоопрокидыванием (RSS), INFOCENTER;
+— опорное устройство GOS 24 т, шкворень OREX 2 дюйма;
+— боковая алюминиевая защита, заднее защитное устройство, 2 ящика SKARB с замком;
+— шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс (с запасным).
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -2116,16 +2173,26 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L Fox), 3-х осный, под заказ.
-Осевой агрегат Fox, барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
-6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
-Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
-При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (PT-24L Fox), новый, под заказ. 3 оси.
+Поставка — 15 рабочих дней с момента предоплаты.
+Условия
+— заводская гарантия 12 месяцев;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
+Технические характеристики
+— осевой агрегат Fox, барабанные тормоза, нагрузка на ось 9 000 кг;
+— усиленная пневмоподвеска с подъёмом/опусканием, манометр давления;
+— тормозная система TEBS 2S/2M с противоопрокидыванием (RSS);
+— 6 пар коников с неоткрепляемыми стойками, по 7 т, регулируются вдоль рамы; внутренняя высота коника 2 340 мм; 6 ремней;
+— передняя стенка неразборная, перфорированная, с крюками для каната и креплением для лома и лопаты;
+— опорное устройство GOS 24 т, шкворень OREX 2 дюйма;
+— боковая алюминиевая противоподкатная защита, металлический ящик с замком;
+— шины TYREX 385/65R22,5;
+— максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -2308,14 +2375,21 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
-Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, дисковые тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (PT-24L SAF Heavy Duty), 2024 года, б/у, в наличии. На ходу, полностью исправен, не требует вложений и ремонта.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами;
+— торг при осмотре.
+Технические характеристики
+— усиленное шасси из двутавровых лонжеронов;
+— 3 оси SAF Heavy Duty, дисковые тормоза, пневмоподвеска с подъёмом/опусканием, нагрузка на ось 9 000 кг;
+— тормозная система WABCO TEBS-E с противоопрокидыванием (RSS);
+— шины 385/65R22,5, односкат;
+— 6 пар открепляемых коников по 8 т (сталь STRENX 700MC), регулируются вдоль рамы; внутренняя высота коника 2 330 мм;
+— настил — ламинированная берёзовая фанера; опорное устройство BPW 24 т;
+— максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -2490,32 +2564,25 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины без груза. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Скидка от производителя на линейку бортовых прицепов — 10%.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Характеристики:
-- Борт: Алюминий
-- Длина (внутренние размеры), мм: 13 625
-- Ширина (внутренние размеры), мм: 2480
-- Высота седельно-сцепного устройства, мм: 1 200 / 1 350
-- Масса снаряженного полуприцепа, не более, кг: 6 700
-- Разрешённая максимальная масса, кг: 38 500
-- Нагрузка на ССУ, кг: 11085
-- Осевая нагрузка: 27000
-- Оси: Тонар
-- Шины: бескамерные 385/65R 22,5
-- Подвеска: зависимая, на продольных упругих рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-- Подъёмная ось: Передняя
-- Опорное устройство: на 24 т
-Дополнительно:
-- Задняя стенка: откидной борт
-- Передний борт: металлический, съемный
-- Боковые стенки / борта: откидные, крепятся запорами к стойкам / 8 шт
-- Пол: настил из ламинированной фанеры толщиной 27 мм
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+          <t>Полуприцеп бортовой Тонар B3-13 (9888), новый, под заказ у завода-изготовителя. 13,6 м, три оси, первая подъёмная, со стаканами под коники (коники в комплект не входят).
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— скидка производителя на бортовые полуприцепы — 10%;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
+Технические характеристики
+— борт алюминиевый; боковые борта откидные, 8 шт.; задний — откидной; передний — металлический, съёмный;
+— внутренние размеры 13 625 × 2 480 мм;
+— высота ССУ 1 200 / 1 350 мм, нагрузка на ССУ 11 085 кг;
+— снаряжённая масса не более 6 700 кг, разрешённая максимальная 38 500 кг, осевая нагрузка 27 000 кг;
+— шины бескамерные 385/65R22,5;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— пол — ламинированная фанера 27 мм; опорное устройство на 24 т.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -2702,39 +2769,27 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
-Скидка от производителя на линейку контейнеровозов — 5%.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)
-Характеристики:
-- Количество осей: 4, 1-я и 2-я подъемные
-- Подвеска: рычажного типа
-- ССУ: 1100
-- Тип: полуприцеп-контейнеровоз
-- Тип ошиновки: односкатный
-- Тормозная система: TEBS
-РАЗМЕРЫ:
-- Длина полуприцепа, мм: 12 192
-- Ширина полуприцепа, мм: 2 550
-- Высота полуприцепа, мм: 1 104
-- Высота ССУ, мм: 1 100
-ВЕС:
-- Масса снаряженного полуприцепа, не более, кг: 6 200
-- Разрешенная максимальная масса, кг: 44 000
-- Нагрузка на колесную тележку, кг: 33 000
-- Нагрузка на ССУ, кг: 11 000
-ОСИ:
-- Оси колес: Тонар
-- Шины: бескамерные 385/55R 22.5
-- Подъемные оси: 1-я и 2-я (базовая комплектация)
-- Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Типы перевозимых контейнеров: 20', 2x20', 30', 30' HC, 40', 40'HC
-- Опорное устройство: на 24 т
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, под заказ у завода-изготовителя. 4 оси, передняя вынесена вперёд на 2 560 мм. Есть эта же модель б/у в наличии, дешевле — уточняйте по телефону.
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— скидка производителя на контейнеровозы — 5%;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— оси: 4, 1-я и 2-я подъёмные;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— тормозная система TEBS;
+— шины бескамерные 385/55R22.5, односкатные;
+— контейнеры: 20', 2×20', 30', 30' HC, 40', 40' HC;
+— длина 12 192 мм, ширина 2 550 мм, высота 1 104 мм, высота ССУ 1 100 мм;
+— снаряжённая масса не более 6 200 кг, разрешённая максимальная 44 000 кг;
+— нагрузка на колёсную тележку 33 000 кг, на ССУ 11 000 кг;
+— опорное устройство на 24 т.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2921,11 +2976,21 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), 2023 года, б/у. В работе, полностью исправен.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— возможна аренда с правом выкупа;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами.
+Технические характеристики
+— оси: 4, тройная задняя тележка и вынесенная вперёд ось;
+— тормоза дисковые, пневмопривод;
+— подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами;
+— шины 385/55R22.5, односкатные;
+— контейнеры: 20', 2×20', 30', 30' HC, 40', 40' HC;
+— разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг;
+— нагрузка на ССУ 11 000 кг, высота ССУ 1 100 мм.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -3100,14 +3165,22 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
-Действует скидка — уточняйте у менеджера.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
-Гарантия завода — 3 года.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— гарантия завода 3 года;
+— акция до 31 октября — уточняйте условия у менеджера;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
+— подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые;
+— шины 385/55R22.5, односкатные; высота ССУ 1 100 мм;
+— контейнеры: 20', 2×20', 30', 30' HC, 40', 40' HC;
+— разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
@@ -3294,14 +3367,22 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
-Действует скидка — уточняйте у менеджера.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
-Гарантия завода — 3 года.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— гарантия завода 3 года;
+— акция до 31 октября — уточняйте условия у менеджера;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
+— подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые;
+— шины 385/55R22.5, односкатные; высота ССУ 1 100 мм;
+— контейнеры: 20', 2×20', 30', 30' HC, 40', 40' HC;
+— разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
@@ -3488,14 +3569,22 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>Новый полуприцеп-контейнеровоз Тонар K4-U (99891), 2026 года. В наличии три таких контейнеровоза, ЭПТС оформлены — можно забрать сразу.
-Действует скидка — уточняйте у менеджера.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось. 1-я и 2-я оси подъёмные — меньше износ шин и расход топлива при движении без груза. Подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые. Шины 385/55R22.5, односкатные. Высота ССУ 1 100 мм.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
-Гарантия завода — 3 года.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— гарантия завода 3 года;
+— акция до 31 октября — уточняйте условия у менеджера;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
+— подвеска на продольных рычагах с пневмоэлементами, тормоза дисковые;
+— шины 385/55R22.5, односкатные; высота ССУ 1 100 мм;
+— контейнеры: 20', 2×20', 30', 30' HC, 40', 40' HC;
+— разрешённая максимальная масса 44 000 кг, снаряжённая 6 200 кг, нагрузка на ССУ 11 000 кг.
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
@@ -3682,42 +3771,26 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ без груза. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
-Скидка от производителя на линейку лесовозов — 5%.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Характеристики:
-- Количество осей: 3, 1-я подъемная
-- Кузов: коники разборные
-- Объем: геометрический объём перевозимого груза: 63 куб.м
-- Подвеска: рычажного типа
-- ССУ: 1 150 / 1 250 / 1 350
-- Тип: полуприцеп-сортиментовоз для перевозки длинномерных грузов
-- Тип ошиновки: односкатный
-- Тормозная система: TEBS
-РАЗМЕРЫ:
-- Длина полуприцепа, мм: 12800
-- Ширина полуприцепа, мм: 2550
-- Высота полуприцепа, мм: 3 770 / 3 870 / 3 970
-- Высота седельно-сцепного устройства, мм: 1 150 / 1 250 / 1 350
-ВЕС:
-- Осевая нагрузка, кг: 27000
-- Масса снаряженного полуприцепа, не более, кг: 6300
-- Технически допустимая максимальная масса полуприцепа, кг: 43000
-- Нагрузка на ССУ, кг: 15900
-ОСИ:
-- Оси колёс: Тонар
-- Шины: бескамерные 385/65R 22,5
-- Подъёмная ось: передняя
-- Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Передний щит: стальной, с усилителями
-- Опорное устройство: на 24 т
-- Геометрический объём перевозимого груза, куб.м: 63
-- Коники: разборные
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), новый, под заказ у завода-изготовителя. 3 оси, первая подъёмная, коники разборные, 6 шт.
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— скидка производителя на лесовозы — 5%;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
+Технические характеристики
+— геометрический объём перевозимого груза 63 м³;
+— длина 12 800 мм, ширина 2 550 мм, высота 3 770 / 3 870 / 3 970 мм;
+— высота ССУ 1 150 / 1 250 / 1 350 мм, нагрузка на ССУ 15 900 кг;
+— снаряжённая масса не более 6 300 кг, технически допустимая максимальная 43 000 кг, осевая нагрузка 27 000 кг;
+— межосевое расстояние 1 310 мм; шины бескамерные 385/65R22,5;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— тормоза барабанные, TEBS;
+— передний щит стальной, с усилителями; опорное устройство на 24 т.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
@@ -3908,48 +3981,28 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 86,9 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
-В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины.
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Характеристики:
-- Количество осей: 3
-- Кузов: сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну.
-- Объём: 86,9 куб.м
-- Подвеска: рычажного типа
-- ССУ: 1150
-- Тип: рефрижераторный полуприцеп
-- Тип ошиновки: односкатный
-- Тормозная система: TEBS
-РАЗМЕРЫ:
-- Длина (внутренние размеры), мм: 13 500
-- Ширина (внутренние размеры), мм: 2 465
-- Высота (внутренние размеры), мм: 2 616
-- Высота ССУ, мм: 1150
-ВЕС:
-- Масса снаряженного полуприцепа, не более, кг: 8 600
-- Разрешенная максимальная масса, кг: 38 080
-- Нагрузка на колёсную тележку, кг: 27 000
-- Нагрузка на ССУ, кг: 10 870
-ОСИ:
-- Оси колес: Тонар
-- Шины: бескамерные 385/65 R22.5
-- Подъемные оси: 1-ая (базовая комплектация)
-- Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-ПРЕИМУЩЕСТВА:
-- Облегчённая рама из высокопрочной стали, модульная: при повреждении меняется только неисправная секция.
-- Цинкование рамы защищает ее от влаги, реагентов и соли, гарантируя исключительную долговечность, даже в суровых условиях.
-ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Объём кузова, куб.м: 86,9
-- Количество европалет, шт: 33
-- Задняя стенка: двустворчатая дверь, каждая створка на 3-х петлях; двойные поворотные штанговые запоры; 3-х уровневый резиновый уплотнитель; рама заднего проема из нержавеющей стали
-- Боковые стенки: сэндвич-панели с усиленной жесткостью
-- Пол: герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
-- Опорное устройство: на 24 т
-- Крыша: сэндвич-панели; 6 потолочных светодиодных фонарей внутреннего освещения обеспечивают высокую яркость и низкое энергопотребление
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-рефрижератор Тонар R3-13, новый, под заказ у завода-изготовителя. 13,6 м, 3 оси, первая подъёмная, 33 европаллеты. Доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути.
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— кузов из сэндвич-панелей, объём 86,9 м³; пол герметичный, из сэндвич-панели, настил — рифлёный алюминий;
+— внутренние размеры 13 500 × 2 465 × 2 616 мм;
+— задняя дверь двустворчатая, по 3 петли на створку, двойные поворотные штанговые запоры, 3-уровневый уплотнитель, рама проёма из нержавеющей стали;
+— крыша из сэндвич-панелей, 6 светодиодных потолочных фонарей;
+— снаряжённая масса не более 8 600 кг, разрешённая максимальная 38 080 кг;
+— нагрузка на колёсную тележку 27 000 кг, на ССУ 10 870 кг; высота ССУ 1 150 мм;
+— оси дисковые; шины бескамерные 385/65R22,5;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— тормозная система TEBS;
+— рама облегчённая, из высокопрочной стали, модульная, оцинкованная;
+— опорное устройство на 24 т.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
@@ -4136,48 +4189,26 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Характеристики:
-- Количество осей: 4
-- Кузов: полукруглый кузов, выполнен из высокопрочных сталей
-- Объем: 34
-- Подвеска: рычажного типа
-- ССУ: 1150
-- Тент: с механическим приводом, входит в базовую комплектацию
-- Тип: облегченный полуприцеп-самосвал
-- Тип ошиновки: односкатная
-- Тормозная система: TEBS
-РАЗМЕРЫ:
-- Ширина кузова, мм: 2550
-- Высота, мм: 3157
-- Высота седельно-сцепного устройства, мм: 1150
-- Длина кузова, мм: 10110
-ВЕС:
-- Масса перевозимого груза, кг: 28550
-- Нагрузка на ССУ, кг: 9650
-- Осевая нагрузка, кг: 26800
-- Масса снаряженного полуприцепа, не более, кг: 7900
-ОСИ:
-- Шины: бескамерные 385/65R 22,5
-- Подъемная ось: 1 и 2
-- Оси колес: Тонар
-- Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-ПРЕИМУЩЕСТВА:
-- Снаряженная масса 7 900 кг.
-- Габаритная высота не превышает 3,2 метра (!).
-ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Задний борт: откидной, с лючком с возможностью регулировки разгрузки
-- Тент: с механическим приводом, входит в базовую комплектацию
-- Опорное устройство: на 24 т
-- Угол подъема кузова, град: 45
-- Колея колес, мм: 2 040
-- Объем кузова, куб.м: 34
-- Минимальный объем масляного бака тягача, л: 150
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп самосвальный Тонар SH4-34 (9595), новый, под заказ у завода-изготовителя. Задняя разгрузка, облегчённый, 4 оси, кузов 33,6 м³ полукруглой формы — сыпучий груз сходит легче, в том числе влажный. Под сыпучие строительные материалы.
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— тент с механическим приводом в базовой комплектации; задний борт откидной, с лючком регулировки разгрузки;
+— длина кузова 10 110 мм, ширина 2 550 мм, высота 3 157 мм (габаритная — не более 3,2 м);
+— высота ССУ 1 150 мм, нагрузка на ССУ 9 650 кг;
+— снаряжённая масса не более 7 900 кг, масса перевозимого груза 28 550 кг, осевая нагрузка 26 800 кг;
+— подъёмные оси 1-я и 2-я; шины бескамерные 385/65R22,5;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— тормоза барабанные, TEBS;
+— угол подъёма кузова 45°, колея 2 040 мм; опорное устройство на 24 т;
+— минимальный объём масляного бака тягача 150 л.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -4364,13 +4395,21 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
-Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+          <t>Полуприцеп со сдвижным полом Тонар SDP4-89 (95895), новый, под заказ у завода-изготовителя. Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без подъёма кузова — можно разгружаться на неровных площадках и под низкими навесами. Под насыпные грузы: щепа, зерно, песок и т. п.
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— оси: 4, первая вынесенная;
+— алюминиевый кузов, объём 89 м³;
+— габаритная длина 14,6 м, погрузочная длина 14,1 м;
+— высота ССУ 1 150 мм.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -4557,50 +4596,29 @@
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Скидка от производителя на линейку шторных прицепов — 10%.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Характеристики:
-- Количество осей: 3
-- Кузов: со сдвижной крышей и сдвижными боковинами; с элементами крепления груза
-- Объем: 92 куб.м.
-- Подвеска: рычажного типа
-- ССУ: 1150
-- Тип: шторно-бортовой полуприцеп
-- Тип ошиновки: односкатный
-- Тормозная система: TEBS
-Опции:
-- Дополнительные опции: TIR-исполнение, коники с ящиком для хранения
-РАЗМЕРЫ:
-- Длина (внутренние размеры), мм: 13600
-- Ширина (внутренние размеры), мм: 2480
-- Высота (внутренние размеры), мм: 2700
-- Высота седельно-сцепного устройства, мм: 1150
-ВЕС:
-- Масса снаряженного полуприцепа, не более, кг: 7300
-- Разрешённая максимальная масса, кг: 38300
-- Нагрузка на ССУ, кг: 11085
-- Нагрузка на колёсную тележку, кг: 27000
-ОСИ:
-- Оси колес: Тонар
-- Шины: бескамерные 385/65R 22,5
-- Подъёмная ось: передняя
-- Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-ПРЕИМУЩЕСТВА:
-- Алюминиевые борта обладают повышенной стойкостью к коррозии и различным воздействиям внешней среды
-ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Крыша: сдвижная крыша с возможностью верхней загрузки
-- Боковые стенки / борта: шторного типа / алюминиевые, 8 шт
-- Объём кузова, куб.м: 91,4
-- Опорное устройство: на 24 т
-- Задняя стенка: оборудована распашной двустворчатой алюминиевой дверью; на каждой двери по 2 запорных устройства
-- Пол: настил из ламинированной фанеры толщиной 27 мм
-ГРУЗОПОДЪЁМНОСТЬ:
-- Перевозка грузов массой до 31 000 килограммов
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).</t>
+          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), новый, под заказ у завода-изготовителя. 13,6 м, 3 оси, первая подъёмная, со стаканами под коники (коники в комплект не входят).
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— скидка производителя на шторные полуприцепы — 10%;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
+Технические характеристики
+— крыша сдвижная, с возможностью верхней загрузки; боковины — шторы и алюминиевые борта, 8 шт.;
+— задняя дверь алюминиевая, распашная, по 2 запора на створку;
+— объём кузова 91,4 м³; внутренние размеры 13 600 × 2 480 × 2 700 мм;
+— грузоподъёмность до 31 000 кг;
+— снаряжённая масса не более 7 300 кг, разрешённая максимальная 38 300 кг;
+— нагрузка на колёсную тележку 27 000 кг, на ССУ 11 085 кг; высота ССУ 1 150 мм;
+— оси дисковые; шины бескамерные 385/65R22,5;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— тормозная система TEBS;
+— пол — ламинированная фанера 27 мм; опорное устройство на 24 т;
+— доступные опции: TIR-исполнение, коники с ящиком для хранения.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N21" s="1" t="inlineStr">
@@ -4791,44 +4809,27 @@
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый прямоугольный кузов, объём 50 м³, до 33,2 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными лючками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽).
-Гарантия завода — 3 года. Поставка после согласования комплектации.
-Характеристики:
-- Количество осей: 3, 1-я подъёмная
-- Кузов: алюминиевый прямоугольный; комбинированный задний борт (откидной и распашной) с разгрузочными лючками
-- Объём кузова: 50 куб.м
-- Подвеска: рычажного типа
-- ССУ: 1200
-- Тент: с механическим приводом, входит в базовую комплектацию
-- Тип: самосвальный полуприцеп-зерновоз
-- Тип ошиновки: односкатная
-- Тормозная система: TEBS
-- Дополнительные опции: установка надставных бортов
-РАЗМЕРЫ:
-- Длина кузова, мм: 12 166
-- Ширина кузова, мм: 2 550
-- Высота, мм: 3 621
-- Высота седельно-сцепного устройства, мм: 1 200
-ВЕС:
-- Масса снаряженного полуприцепа, не более, кг: 7 600
-- Масса перевозимого груза, кг: 33 200
-- Нагрузка на ССУ, кг: 14 000
-- Осевая нагрузка, кг: 27 000
-ОСИ:
-- Оси колёс: Тонар
-- Шины: бескамерные 385/65R 22,5
-- Подъёмная ось: передняя
-- Подвеска: зависимая, на продольных рычагах с пневматическими упругими элементами и телескопическими гидравлическими амортизаторами
-ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:
-- Боковые борта: из алюминиевого профиля
-- Колея колёс, мм: 2 040
-- Опорное устройство: на 24 т
-- Угол подъёма кузова, град: 45
-- Минимальный объём масляного бака тягача, л: 150
-Доставка по России.
-Лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др. Работаем с юридическими и физическими лицами.
-Подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).</t>
+          <t>Полуприцеп-зерновоз Тонар 95941, новый, под заказ у завода-изготовителя. Задняя разгрузка, алюминиевый прямоугольный кузов 50 м³, до 33,2 т груза, 3 оси (первая подъёмная). Насыпные зерновые, комбикорм и паллетированный груз.
+Поставка после согласования комплектации.
+Условия
+— гарантия завода 3 года;
+— при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— доставка по России;
+— работаем с юридическими и физическими лицами;
+— подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
+Технические характеристики
+— тент с механическим приводом в базовой комплектации;
+— задний борт комбинированный (откидной и распашной), с разгрузочными лючками; боковые борта — алюминиевый профиль;
+— длина кузова 12 166 мм, ширина 2 550 мм, высота 3 621 мм;
+— высота ССУ 1 200 мм, нагрузка на ССУ 14 000 кг;
+— снаряжённая масса не более 7 600 кг, масса перевозимого груза 33 200 кг, осевая нагрузка 27 000 кг;
+— шины бескамерные 385/65R22,5;
+— оси Тонар; подвеска зависимая, на продольных рычагах с пневмоэлементами и телескопическими амортизаторами;
+— тормозная система TEBS;
+— угол подъёма кузова 45°, колея 2 040 мм; опорное устройство на 24 т; масляный бак тягача от 150 л;
+— опция: надставные борта.
+Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
@@ -5015,11 +5016,22 @@
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход без груза. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
-Возможна покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.</t>
+          <t>Полуприцеп шторный V-Trailer 329D, 2023 года, б/у. В работе, полностью исправен.
+Осмотр: Москва, Ижорская ул., 15с2.
+Условия
+— возможна аренда с правом выкупа;
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими и физическими лицами.
+Технические характеристики
+— 13,6 × 2,5 × 4 м, 91 м³; полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте;
+— оси SAF, передняя подъёмная;
+— опорное устройство JOST 24 т, шкворень 2 дюйма (ISO 1726);
+— пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 т;
+— крыша сдвижная (Sesam/Edscha) — загрузка сверху краном или погрузчиком без снятия тента;
+— двери алюминиевые BPW Smartmaster II, передний и задний порталы стальные;
+— рама облегчённая, с усилениями против скручивания; корзины под коники, по 7 на сторону;
+— тент: борта 900 г/м², крыша 680 г/м².
+Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -417,7 +417,7 @@
   <dimension ref="A1:BE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
@@ -1746,7 +1746,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Ставропольский край, с. Надежда, ул. Ставропольская, 83</t>
+          <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -417,7 +417,7 @@
   <dimension ref="A1:BE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
@@ -1746,17 +1746,17 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15с2</t>
+          <t>Ставропольский край, Шпаковский муниципальный округ, с. Надежда, Ставропольская ул., 83</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>55.8958019</t>
+          <t>45.0572985</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>37.5237956</t>
+          <t>42.0957436</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3165,7 +3165,8 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
+          <t>Цена 2 940 000 ₽ при любой оплате (прайс завода 3 200 000 ₽).
+Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — гарантия завода 3 года;
@@ -3367,7 +3368,8 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
+          <t>Цена 2 940 000 ₽ при любой оплате (прайс завода 3 200 000 ₽).
+Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — гарантия завода 3 года;
@@ -3569,7 +3571,8 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
+          <t>Цена 2 940 000 ₽ при любой оплате (прайс завода 3 200 000 ₽).
+Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — гарантия завода 3 года;

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE23"/>
+  <dimension ref="A1:BE22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>tonar-b313-9888</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -2374,195 +2374,6 @@
         </is>
       </c>
       <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (PT-24L SAF Heavy Duty), 2024 года, б/у, в наличии. На ходу, полностью исправен, не требует вложений и ремонта.
-Осмотр: Москва, Ижорская ул., 15с2.
-Условия
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами;
-— торг при осмотре.
-Технические характеристики
-— усиленное шасси из двутавровых лонжеронов;
-— 3 оси SAF Heavy Duty, дисковые тормоза, пневмоподвеска с подъёмом/опусканием, нагрузка на ось 9 000 кг;
-— тормозная система WABCO TEBS-E с противоопрокидыванием (RSS);
-— шины 385/65R22,5, односкат;
-— 6 пар открепляемых коников по 8 т (сталь STRENX 700MC), регулируются вдоль рамы; внутренняя высота коника 2 330 мм;
-— настил — ламинированная берёзовая фанера; опорное устройство BPW 24 т;
-— максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>2970000</t>
-        </is>
-      </c>
-      <c r="P10" s="1" t="inlineStr"/>
-      <c r="Q10" s="1" t="inlineStr"/>
-      <c r="R10" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
-        </is>
-      </c>
-      <c r="S10" s="1" t="inlineStr"/>
-      <c r="T10" s="1" t="inlineStr"/>
-      <c r="U10" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15с2</t>
-        </is>
-      </c>
-      <c r="V10" s="1" t="inlineStr"/>
-      <c r="W10" s="1" t="inlineStr"/>
-      <c r="X10" s="1" t="inlineStr">
-        <is>
-          <t>Прицепы</t>
-        </is>
-      </c>
-      <c r="Y10" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="Z10" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AA10" s="1" t="inlineStr"/>
-      <c r="AB10" s="1" t="inlineStr">
-        <is>
-          <t>2970000</t>
-        </is>
-      </c>
-      <c r="AC10" s="1" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD10" s="1" t="inlineStr"/>
-      <c r="AE10" s="1" t="inlineStr"/>
-      <c r="AF10" s="1" t="inlineStr"/>
-      <c r="AG10" s="1" t="inlineStr"/>
-      <c r="AH10" s="1" t="inlineStr"/>
-      <c r="AI10" s="1" t="inlineStr"/>
-      <c r="AJ10" s="1" t="inlineStr"/>
-      <c r="AK10" s="1" t="inlineStr"/>
-      <c r="AL10" s="1" t="inlineStr"/>
-      <c r="AM10" s="1" t="inlineStr">
-        <is>
-          <t>С пробегом</t>
-        </is>
-      </c>
-      <c r="AN10" s="1" t="inlineStr"/>
-      <c r="AO10" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AP10" s="1" t="inlineStr">
-        <is>
-          <t>Steelbear</t>
-        </is>
-      </c>
-      <c r="AQ10" s="1" t="inlineStr">
-        <is>
-          <t>PL-24L</t>
-        </is>
-      </c>
-      <c r="AR10" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AS10" s="1" t="inlineStr">
-        <is>
-          <t>Лесовоз (сортиментовоз)</t>
-        </is>
-      </c>
-      <c r="AT10" s="1" t="inlineStr"/>
-      <c r="AU10" s="1" t="inlineStr"/>
-      <c r="AV10" s="1" t="inlineStr">
-        <is>
-          <t>XWZ9412LLR1202021</t>
-        </is>
-      </c>
-      <c r="AW10" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AX10" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AY10" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
-      <c r="AZ10" s="1" t="inlineStr">
-        <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="BA10" s="1" t="inlineStr">
-        <is>
-          <t>37100</t>
-        </is>
-      </c>
-      <c r="BB10" s="1" t="inlineStr">
-        <is>
-          <t>13620</t>
-        </is>
-      </c>
-      <c r="BC10" s="1" t="inlineStr"/>
-      <c r="BD10" s="1" t="inlineStr"/>
-      <c r="BE10" s="1" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15с2</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>55.8958019</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>37.5237956</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>tonar-b313-9888</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>79685590315</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп бортовой Тонар B3-13 (9888), новый, под заказ у завода-изготовителя. 13,6 м, три оси, первая подъёмная, со стаканами под коники (коники в комплект не входят).
 Поставка после согласования комплектации.
@@ -2585,189 +2396,189 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="O10" s="1" t="inlineStr">
         <is>
           <t>3150000</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr"/>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="P10" s="1" t="inlineStr"/>
+      <c r="Q10" s="1" t="inlineStr"/>
+      <c r="R10" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr"/>
-      <c r="T11" s="1" t="inlineStr"/>
-      <c r="U11" s="1" t="inlineStr">
+      <c r="S10" s="1" t="inlineStr"/>
+      <c r="T10" s="1" t="inlineStr"/>
+      <c r="U10" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V11" s="1" t="inlineStr"/>
-      <c r="W11" s="1" t="inlineStr"/>
-      <c r="X11" s="1" t="inlineStr">
+      <c r="V10" s="1" t="inlineStr"/>
+      <c r="W10" s="1" t="inlineStr"/>
+      <c r="X10" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Y10" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="Z10" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr"/>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AA10" s="1" t="inlineStr"/>
+      <c r="AB10" s="1" t="inlineStr">
         <is>
           <t>3150000</t>
         </is>
       </c>
-      <c r="AC11" s="1" t="inlineStr">
+      <c r="AC10" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD11" s="1" t="inlineStr">
+      <c r="AD10" s="1" t="inlineStr">
         <is>
           <t>315000</t>
         </is>
       </c>
-      <c r="AE11" s="1" t="inlineStr"/>
-      <c r="AF11" s="1" t="inlineStr">
+      <c r="AE10" s="1" t="inlineStr"/>
+      <c r="AF10" s="1" t="inlineStr">
         <is>
           <t>315000</t>
         </is>
       </c>
-      <c r="AG11" s="1" t="inlineStr">
+      <c r="AG10" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH11" s="1" t="inlineStr"/>
-      <c r="AI11" s="1" t="inlineStr">
+      <c r="AH10" s="1" t="inlineStr"/>
+      <c r="AI10" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ11" s="1" t="inlineStr"/>
-      <c r="AK11" s="1" t="inlineStr"/>
-      <c r="AL11" s="1" t="inlineStr"/>
-      <c r="AM11" s="1" t="inlineStr">
+      <c r="AJ10" s="1" t="inlineStr"/>
+      <c r="AK10" s="1" t="inlineStr"/>
+      <c r="AL10" s="1" t="inlineStr"/>
+      <c r="AM10" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN11" s="1" t="inlineStr"/>
-      <c r="AO11" s="1" t="inlineStr">
+      <c r="AN10" s="1" t="inlineStr"/>
+      <c r="AO10" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP11" s="1" t="inlineStr">
+      <c r="AP10" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ11" s="1" t="inlineStr">
+      <c r="AQ10" s="1" t="inlineStr">
         <is>
           <t>B3-13 (9888)</t>
         </is>
       </c>
-      <c r="AR11" s="1" t="inlineStr">
+      <c r="AR10" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS11" s="1" t="inlineStr">
+      <c r="AS10" s="1" t="inlineStr">
         <is>
           <t>Бортовой</t>
         </is>
       </c>
-      <c r="AT11" s="1" t="inlineStr"/>
-      <c r="AU11" s="1" t="inlineStr"/>
-      <c r="AV11" s="1" t="inlineStr"/>
-      <c r="AW11" s="1" t="inlineStr">
+      <c r="AT10" s="1" t="inlineStr"/>
+      <c r="AU10" s="1" t="inlineStr"/>
+      <c r="AV10" s="1" t="inlineStr"/>
+      <c r="AW10" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX11" s="1" t="inlineStr">
+      <c r="AX10" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AY11" s="1" t="inlineStr">
+      <c r="AY10" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ11" s="1" t="inlineStr">
+      <c r="AZ10" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="BA11" s="1" t="inlineStr">
+      <c r="BA10" s="1" t="inlineStr">
         <is>
           <t>31600</t>
         </is>
       </c>
-      <c r="BB11" s="1" t="inlineStr">
+      <c r="BB10" s="1" t="inlineStr">
         <is>
           <t>13600</t>
         </is>
       </c>
-      <c r="BC11" s="1" t="inlineStr"/>
-      <c r="BD11" s="1" t="inlineStr"/>
-      <c r="BE11" s="1" t="inlineStr"/>
+      <c r="BC10" s="1" t="inlineStr"/>
+      <c r="BD10" s="1" t="inlineStr"/>
+      <c r="BE10" s="1" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-99891-order</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr"/>
-      <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="inlineStr"/>
-      <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr"/>
+      <c r="F11" s="1" t="inlineStr"/>
+      <c r="G11" s="1" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, под заказ у завода-изготовителя. 4 оси, передняя вынесена вперёд на 2 560 мм. Есть эта же модель б/у в наличии, дешевле — уточняйте по телефону.
 Поставка после согласования комплектации.
@@ -2792,189 +2603,189 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>3200000</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr"/>
-      <c r="Q12" s="1" t="inlineStr"/>
-      <c r="R12" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr"/>
+      <c r="Q11" s="1" t="inlineStr"/>
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
         </is>
       </c>
-      <c r="S12" s="1" t="inlineStr"/>
-      <c r="T12" s="1" t="inlineStr"/>
-      <c r="U12" s="1" t="inlineStr">
+      <c r="S11" s="1" t="inlineStr"/>
+      <c r="T11" s="1" t="inlineStr"/>
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V12" s="1" t="inlineStr"/>
-      <c r="W12" s="1" t="inlineStr"/>
-      <c r="X12" s="1" t="inlineStr">
+      <c r="V11" s="1" t="inlineStr"/>
+      <c r="W11" s="1" t="inlineStr"/>
+      <c r="X11" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr"/>
-      <c r="AB12" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr"/>
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>3200000</t>
         </is>
       </c>
-      <c r="AC12" s="1" t="inlineStr">
+      <c r="AC11" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD12" s="1" t="inlineStr">
+      <c r="AD11" s="1" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="AE12" s="1" t="inlineStr"/>
-      <c r="AF12" s="1" t="inlineStr">
+      <c r="AE11" s="1" t="inlineStr"/>
+      <c r="AF11" s="1" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="AG12" s="1" t="inlineStr">
+      <c r="AG11" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH12" s="1" t="inlineStr"/>
-      <c r="AI12" s="1" t="inlineStr">
+      <c r="AH11" s="1" t="inlineStr"/>
+      <c r="AI11" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ12" s="1" t="inlineStr"/>
-      <c r="AK12" s="1" t="inlineStr"/>
-      <c r="AL12" s="1" t="inlineStr"/>
-      <c r="AM12" s="1" t="inlineStr">
+      <c r="AJ11" s="1" t="inlineStr"/>
+      <c r="AK11" s="1" t="inlineStr"/>
+      <c r="AL11" s="1" t="inlineStr"/>
+      <c r="AM11" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN12" s="1" t="inlineStr"/>
-      <c r="AO12" s="1" t="inlineStr">
+      <c r="AN11" s="1" t="inlineStr"/>
+      <c r="AO11" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP12" s="1" t="inlineStr">
+      <c r="AP11" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ12" s="1" t="inlineStr">
+      <c r="AQ11" s="1" t="inlineStr">
         <is>
           <t>K4-U (99891)</t>
         </is>
       </c>
-      <c r="AR12" s="1" t="inlineStr">
+      <c r="AR11" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS12" s="1" t="inlineStr">
+      <c r="AS11" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AT12" s="1" t="inlineStr"/>
-      <c r="AU12" s="1" t="inlineStr"/>
-      <c r="AV12" s="1" t="inlineStr"/>
-      <c r="AW12" s="1" t="inlineStr">
+      <c r="AT11" s="1" t="inlineStr"/>
+      <c r="AU11" s="1" t="inlineStr"/>
+      <c r="AV11" s="1" t="inlineStr"/>
+      <c r="AW11" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX12" s="1" t="inlineStr">
+      <c r="AX11" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY12" s="1" t="inlineStr">
+      <c r="AY11" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ12" s="1" t="inlineStr">
+      <c r="AZ11" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="BA12" s="1" t="inlineStr">
+      <c r="BA11" s="1" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="BB12" s="1" t="inlineStr">
+      <c r="BB11" s="1" t="inlineStr">
         <is>
           <t>12192</t>
         </is>
       </c>
-      <c r="BC12" s="1" t="inlineStr"/>
-      <c r="BD12" s="1" t="inlineStr"/>
-      <c r="BE12" s="1" t="inlineStr"/>
+      <c r="BC11" s="1" t="inlineStr"/>
+      <c r="BD11" s="1" t="inlineStr"/>
+      <c r="BE11" s="1" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-p0002033</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr"/>
-      <c r="F13" s="1" t="inlineStr"/>
-      <c r="G13" s="1" t="inlineStr"/>
-      <c r="H13" s="1" t="inlineStr"/>
-      <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
+      <c r="G12" s="1" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-контейнеровоз Тонар K4-U (99891), 2023 года, б/у. В работе, полностью исправен.
 Осмотр: Москва, Ижорская ул., 15с2.
@@ -2993,177 +2804,177 @@
 Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>1690000</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr"/>
-      <c r="Q13" s="1" t="inlineStr"/>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="P12" s="1" t="inlineStr"/>
+      <c r="Q12" s="1" t="inlineStr"/>
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr"/>
-      <c r="T13" s="1" t="inlineStr"/>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="S12" s="1" t="inlineStr"/>
+      <c r="T12" s="1" t="inlineStr"/>
+      <c r="U12" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr"/>
-      <c r="W13" s="1" t="inlineStr"/>
-      <c r="X13" s="1" t="inlineStr">
+      <c r="V12" s="1" t="inlineStr"/>
+      <c r="W12" s="1" t="inlineStr"/>
+      <c r="X12" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr"/>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr"/>
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>1690000</t>
         </is>
       </c>
-      <c r="AC13" s="1" t="inlineStr">
+      <c r="AC12" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD13" s="1" t="inlineStr"/>
-      <c r="AE13" s="1" t="inlineStr"/>
-      <c r="AF13" s="1" t="inlineStr"/>
-      <c r="AG13" s="1" t="inlineStr"/>
-      <c r="AH13" s="1" t="inlineStr"/>
-      <c r="AI13" s="1" t="inlineStr"/>
-      <c r="AJ13" s="1" t="inlineStr"/>
-      <c r="AK13" s="1" t="inlineStr"/>
-      <c r="AL13" s="1" t="inlineStr"/>
-      <c r="AM13" s="1" t="inlineStr">
+      <c r="AD12" s="1" t="inlineStr"/>
+      <c r="AE12" s="1" t="inlineStr"/>
+      <c r="AF12" s="1" t="inlineStr"/>
+      <c r="AG12" s="1" t="inlineStr"/>
+      <c r="AH12" s="1" t="inlineStr"/>
+      <c r="AI12" s="1" t="inlineStr"/>
+      <c r="AJ12" s="1" t="inlineStr"/>
+      <c r="AK12" s="1" t="inlineStr"/>
+      <c r="AL12" s="1" t="inlineStr"/>
+      <c r="AM12" s="1" t="inlineStr">
         <is>
           <t>С пробегом</t>
         </is>
       </c>
-      <c r="AN13" s="1" t="inlineStr"/>
-      <c r="AO13" s="1" t="inlineStr">
+      <c r="AN12" s="1" t="inlineStr"/>
+      <c r="AO12" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP13" s="1" t="inlineStr">
+      <c r="AP12" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ13" s="1" t="inlineStr">
+      <c r="AQ12" s="1" t="inlineStr">
         <is>
           <t>K4-U (99891)</t>
         </is>
       </c>
-      <c r="AR13" s="1" t="inlineStr">
+      <c r="AR12" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS13" s="1" t="inlineStr">
+      <c r="AS12" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AT13" s="1" t="inlineStr"/>
-      <c r="AU13" s="1" t="inlineStr"/>
-      <c r="AV13" s="1" t="inlineStr">
+      <c r="AT12" s="1" t="inlineStr"/>
+      <c r="AU12" s="1" t="inlineStr"/>
+      <c r="AV12" s="1" t="inlineStr">
         <is>
           <t>X0T998910P0002033</t>
         </is>
       </c>
-      <c r="AW13" s="1" t="inlineStr">
+      <c r="AW12" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AX13" s="1" t="inlineStr">
+      <c r="AX12" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY13" s="1" t="inlineStr">
+      <c r="AY12" s="1" t="inlineStr">
         <is>
           <t>Рессорная</t>
         </is>
       </c>
-      <c r="AZ13" s="1" t="inlineStr">
+      <c r="AZ12" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA13" s="1" t="inlineStr">
+      <c r="BA12" s="1" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="BB13" s="1" t="inlineStr">
+      <c r="BB12" s="1" t="inlineStr">
         <is>
           <t>12725</t>
         </is>
       </c>
-      <c r="BC13" s="1" t="inlineStr"/>
-      <c r="BD13" s="1" t="inlineStr"/>
-      <c r="BE13" s="1" t="inlineStr"/>
+      <c r="BC12" s="1" t="inlineStr"/>
+      <c r="BD12" s="1" t="inlineStr"/>
+      <c r="BE12" s="1" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-t0004011</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr"/>
-      <c r="F14" s="1" t="inlineStr"/>
-      <c r="G14" s="1" t="inlineStr"/>
-      <c r="H14" s="1" t="inlineStr"/>
-      <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+      <c r="G13" s="1" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>Цена 2 940 000 ₽ при любой оплате (прайс завода 3 200 000 ₽).
 Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
@@ -3184,189 +2995,189 @@
 Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>3040000</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr"/>
-      <c r="R14" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr"/>
+      <c r="Q13" s="1" t="inlineStr"/>
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004011/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004011/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004011/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004011/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004011/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004011/06.jpg</t>
         </is>
       </c>
-      <c r="S14" s="1" t="inlineStr"/>
-      <c r="T14" s="1" t="inlineStr"/>
-      <c r="U14" s="1" t="inlineStr">
+      <c r="S13" s="1" t="inlineStr"/>
+      <c r="T13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V14" s="1" t="inlineStr"/>
-      <c r="W14" s="1" t="inlineStr"/>
-      <c r="X14" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr"/>
+      <c r="W13" s="1" t="inlineStr"/>
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y14" s="1" t="inlineStr">
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z14" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA14" s="1" t="inlineStr"/>
-      <c r="AB14" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr"/>
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>3040000</t>
         </is>
       </c>
-      <c r="AC14" s="1" t="inlineStr">
+      <c r="AC13" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD14" s="1" t="inlineStr">
+      <c r="AD13" s="1" t="inlineStr">
         <is>
           <t>364000</t>
         </is>
       </c>
-      <c r="AE14" s="1" t="inlineStr"/>
-      <c r="AF14" s="1" t="inlineStr"/>
-      <c r="AG14" s="1" t="inlineStr">
+      <c r="AE13" s="1" t="inlineStr"/>
+      <c r="AF13" s="1" t="inlineStr"/>
+      <c r="AG13" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH14" s="1" t="inlineStr"/>
-      <c r="AI14" s="1" t="inlineStr">
+      <c r="AH13" s="1" t="inlineStr"/>
+      <c r="AI13" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ14" s="1" t="inlineStr"/>
-      <c r="AK14" s="1" t="inlineStr"/>
-      <c r="AL14" s="1" t="inlineStr"/>
-      <c r="AM14" s="1" t="inlineStr">
+      <c r="AJ13" s="1" t="inlineStr"/>
+      <c r="AK13" s="1" t="inlineStr"/>
+      <c r="AL13" s="1" t="inlineStr"/>
+      <c r="AM13" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN14" s="1" t="inlineStr"/>
-      <c r="AO14" s="1" t="inlineStr">
+      <c r="AN13" s="1" t="inlineStr"/>
+      <c r="AO13" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP14" s="1" t="inlineStr">
+      <c r="AP13" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ14" s="1" t="inlineStr">
+      <c r="AQ13" s="1" t="inlineStr">
         <is>
           <t>K4-U (99891)</t>
         </is>
       </c>
-      <c r="AR14" s="1" t="inlineStr">
+      <c r="AR13" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS14" s="1" t="inlineStr">
+      <c r="AS13" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AT14" s="1" t="inlineStr"/>
-      <c r="AU14" s="1" t="inlineStr"/>
-      <c r="AV14" s="1" t="inlineStr">
+      <c r="AT13" s="1" t="inlineStr"/>
+      <c r="AU13" s="1" t="inlineStr"/>
+      <c r="AV13" s="1" t="inlineStr">
         <is>
           <t>X0T998910T0004011</t>
         </is>
       </c>
-      <c r="AW14" s="1" t="inlineStr">
+      <c r="AW13" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX14" s="1" t="inlineStr">
+      <c r="AX13" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY14" s="1" t="inlineStr">
+      <c r="AY13" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ14" s="1" t="inlineStr">
+      <c r="AZ13" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA14" s="1" t="inlineStr">
+      <c r="BA13" s="1" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="BB14" s="1" t="inlineStr">
+      <c r="BB13" s="1" t="inlineStr">
         <is>
           <t>12725</t>
         </is>
       </c>
-      <c r="BC14" s="1" t="inlineStr"/>
-      <c r="BD14" s="1" t="inlineStr"/>
-      <c r="BE14" s="1" t="inlineStr"/>
+      <c r="BC13" s="1" t="inlineStr"/>
+      <c r="BD13" s="1" t="inlineStr"/>
+      <c r="BE13" s="1" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-t0004012</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr"/>
-      <c r="F15" s="1" t="inlineStr"/>
-      <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" s="1" t="inlineStr"/>
-      <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="M14" s="1" t="inlineStr">
         <is>
           <t>Цена 2 940 000 ₽ при любой оплате (прайс завода 3 200 000 ₽).
 Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
@@ -3387,189 +3198,189 @@
 Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="O14" s="1" t="inlineStr">
         <is>
           <t>3040000</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr"/>
-      <c r="Q15" s="1" t="inlineStr"/>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="P14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004012/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004012/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004012/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004012/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004012/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004012/06.jpg</t>
         </is>
       </c>
-      <c r="S15" s="1" t="inlineStr"/>
-      <c r="T15" s="1" t="inlineStr"/>
-      <c r="U15" s="1" t="inlineStr">
+      <c r="S14" s="1" t="inlineStr"/>
+      <c r="T14" s="1" t="inlineStr"/>
+      <c r="U14" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V15" s="1" t="inlineStr"/>
-      <c r="W15" s="1" t="inlineStr"/>
-      <c r="X15" s="1" t="inlineStr">
+      <c r="V14" s="1" t="inlineStr"/>
+      <c r="W14" s="1" t="inlineStr"/>
+      <c r="X14" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y15" s="1" t="inlineStr">
+      <c r="Y14" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="Z14" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA15" s="1" t="inlineStr"/>
-      <c r="AB15" s="1" t="inlineStr">
+      <c r="AA14" s="1" t="inlineStr"/>
+      <c r="AB14" s="1" t="inlineStr">
         <is>
           <t>3040000</t>
         </is>
       </c>
-      <c r="AC15" s="1" t="inlineStr">
+      <c r="AC14" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD15" s="1" t="inlineStr">
+      <c r="AD14" s="1" t="inlineStr">
         <is>
           <t>364000</t>
         </is>
       </c>
-      <c r="AE15" s="1" t="inlineStr"/>
-      <c r="AF15" s="1" t="inlineStr"/>
-      <c r="AG15" s="1" t="inlineStr">
+      <c r="AE14" s="1" t="inlineStr"/>
+      <c r="AF14" s="1" t="inlineStr"/>
+      <c r="AG14" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH15" s="1" t="inlineStr"/>
-      <c r="AI15" s="1" t="inlineStr">
+      <c r="AH14" s="1" t="inlineStr"/>
+      <c r="AI14" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ15" s="1" t="inlineStr"/>
-      <c r="AK15" s="1" t="inlineStr"/>
-      <c r="AL15" s="1" t="inlineStr"/>
-      <c r="AM15" s="1" t="inlineStr">
+      <c r="AJ14" s="1" t="inlineStr"/>
+      <c r="AK14" s="1" t="inlineStr"/>
+      <c r="AL14" s="1" t="inlineStr"/>
+      <c r="AM14" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN15" s="1" t="inlineStr"/>
-      <c r="AO15" s="1" t="inlineStr">
+      <c r="AN14" s="1" t="inlineStr"/>
+      <c r="AO14" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP15" s="1" t="inlineStr">
+      <c r="AP14" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ15" s="1" t="inlineStr">
+      <c r="AQ14" s="1" t="inlineStr">
         <is>
           <t>K4-U (99891)</t>
         </is>
       </c>
-      <c r="AR15" s="1" t="inlineStr">
+      <c r="AR14" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS15" s="1" t="inlineStr">
+      <c r="AS14" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AT15" s="1" t="inlineStr"/>
-      <c r="AU15" s="1" t="inlineStr"/>
-      <c r="AV15" s="1" t="inlineStr">
+      <c r="AT14" s="1" t="inlineStr"/>
+      <c r="AU14" s="1" t="inlineStr"/>
+      <c r="AV14" s="1" t="inlineStr">
         <is>
           <t>X0T998910T0004012</t>
         </is>
       </c>
-      <c r="AW15" s="1" t="inlineStr">
+      <c r="AW14" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX15" s="1" t="inlineStr">
+      <c r="AX14" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY15" s="1" t="inlineStr">
+      <c r="AY14" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ15" s="1" t="inlineStr">
+      <c r="AZ14" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA15" s="1" t="inlineStr">
+      <c r="BA14" s="1" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="BB15" s="1" t="inlineStr">
+      <c r="BB14" s="1" t="inlineStr">
         <is>
           <t>12725</t>
         </is>
       </c>
-      <c r="BC15" s="1" t="inlineStr"/>
-      <c r="BD15" s="1" t="inlineStr"/>
-      <c r="BE15" s="1" t="inlineStr"/>
+      <c r="BC14" s="1" t="inlineStr"/>
+      <c r="BD14" s="1" t="inlineStr"/>
+      <c r="BE14" s="1" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>tonar-k4u-t0004016</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
-      <c r="G16" s="1" t="inlineStr"/>
-      <c r="H16" s="1" t="inlineStr"/>
-      <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Цена 2 940 000 ₽ при любой оплате (прайс завода 3 200 000 ₽).
 Полуприцеп-контейнеровоз Тонар K4-U (99891), новый, 2026 года. В наличии три, ЭПТС оформлены — можно забрать сразу.
@@ -3590,189 +3401,189 @@
 Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>3040000</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr"/>
-      <c r="Q16" s="1" t="inlineStr"/>
-      <c r="R16" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr"/>
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004016/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004016/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004016/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004016/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004016/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-t0004016/06.jpg</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr"/>
-      <c r="T16" s="1" t="inlineStr"/>
-      <c r="U16" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr"/>
+      <c r="T15" s="1" t="inlineStr"/>
+      <c r="U15" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V16" s="1" t="inlineStr"/>
-      <c r="W16" s="1" t="inlineStr"/>
-      <c r="X16" s="1" t="inlineStr">
+      <c r="V15" s="1" t="inlineStr"/>
+      <c r="W15" s="1" t="inlineStr"/>
+      <c r="X15" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y16" s="1" t="inlineStr">
+      <c r="Y15" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z16" s="1" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA16" s="1" t="inlineStr"/>
-      <c r="AB16" s="1" t="inlineStr">
+      <c r="AA15" s="1" t="inlineStr"/>
+      <c r="AB15" s="1" t="inlineStr">
         <is>
           <t>3040000</t>
         </is>
       </c>
-      <c r="AC16" s="1" t="inlineStr">
+      <c r="AC15" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD16" s="1" t="inlineStr">
+      <c r="AD15" s="1" t="inlineStr">
         <is>
           <t>364000</t>
         </is>
       </c>
-      <c r="AE16" s="1" t="inlineStr"/>
-      <c r="AF16" s="1" t="inlineStr"/>
-      <c r="AG16" s="1" t="inlineStr">
+      <c r="AE15" s="1" t="inlineStr"/>
+      <c r="AF15" s="1" t="inlineStr"/>
+      <c r="AG15" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH16" s="1" t="inlineStr"/>
-      <c r="AI16" s="1" t="inlineStr">
+      <c r="AH15" s="1" t="inlineStr"/>
+      <c r="AI15" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ16" s="1" t="inlineStr"/>
-      <c r="AK16" s="1" t="inlineStr"/>
-      <c r="AL16" s="1" t="inlineStr"/>
-      <c r="AM16" s="1" t="inlineStr">
+      <c r="AJ15" s="1" t="inlineStr"/>
+      <c r="AK15" s="1" t="inlineStr"/>
+      <c r="AL15" s="1" t="inlineStr"/>
+      <c r="AM15" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN16" s="1" t="inlineStr"/>
-      <c r="AO16" s="1" t="inlineStr">
+      <c r="AN15" s="1" t="inlineStr"/>
+      <c r="AO15" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP16" s="1" t="inlineStr">
+      <c r="AP15" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ16" s="1" t="inlineStr">
+      <c r="AQ15" s="1" t="inlineStr">
         <is>
           <t>K4-U (99891)</t>
         </is>
       </c>
-      <c r="AR16" s="1" t="inlineStr">
+      <c r="AR15" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS16" s="1" t="inlineStr">
+      <c r="AS15" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AT16" s="1" t="inlineStr"/>
-      <c r="AU16" s="1" t="inlineStr"/>
-      <c r="AV16" s="1" t="inlineStr">
+      <c r="AT15" s="1" t="inlineStr"/>
+      <c r="AU15" s="1" t="inlineStr"/>
+      <c r="AV15" s="1" t="inlineStr">
         <is>
           <t>X0T998910T0004016</t>
         </is>
       </c>
-      <c r="AW16" s="1" t="inlineStr">
+      <c r="AW15" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX16" s="1" t="inlineStr">
+      <c r="AX15" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY16" s="1" t="inlineStr">
+      <c r="AY15" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ16" s="1" t="inlineStr">
+      <c r="AZ15" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA16" s="1" t="inlineStr">
+      <c r="BA15" s="1" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="BB16" s="1" t="inlineStr">
+      <c r="BB15" s="1" t="inlineStr">
         <is>
           <t>12725</t>
         </is>
       </c>
-      <c r="BC16" s="1" t="inlineStr"/>
-      <c r="BD16" s="1" t="inlineStr"/>
-      <c r="BE16" s="1" t="inlineStr"/>
+      <c r="BC15" s="1" t="inlineStr"/>
+      <c r="BD15" s="1" t="inlineStr"/>
+      <c r="BE15" s="1" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>tonar-l3-9445</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr"/>
-      <c r="F17" s="1" t="inlineStr"/>
-      <c r="G17" s="1" t="inlineStr"/>
-      <c r="H17" s="1" t="inlineStr"/>
-      <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+      <c r="G16" s="1" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="M16" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-сортиментовоз Тонар L3 (9445), новый, под заказ у завода-изготовителя. 3 оси, первая подъёмная, коники разборные, 6 шт.
 Поставка после согласования комплектации.
@@ -3796,193 +3607,193 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="N16" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
+      <c r="O16" s="1" t="inlineStr">
         <is>
           <t>3200000</t>
         </is>
       </c>
-      <c r="P17" s="1" t="inlineStr"/>
-      <c r="Q17" s="1" t="inlineStr"/>
-      <c r="R17" s="1" t="inlineStr">
+      <c r="P16" s="1" t="inlineStr"/>
+      <c r="Q16" s="1" t="inlineStr"/>
+      <c r="R16" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
         </is>
       </c>
-      <c r="S17" s="1" t="inlineStr"/>
-      <c r="T17" s="1" t="inlineStr"/>
-      <c r="U17" s="1" t="inlineStr">
+      <c r="S16" s="1" t="inlineStr"/>
+      <c r="T16" s="1" t="inlineStr"/>
+      <c r="U16" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V17" s="1" t="inlineStr"/>
-      <c r="W17" s="1" t="inlineStr"/>
-      <c r="X17" s="1" t="inlineStr">
+      <c r="V16" s="1" t="inlineStr"/>
+      <c r="W16" s="1" t="inlineStr"/>
+      <c r="X16" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y17" s="1" t="inlineStr">
+      <c r="Y16" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z17" s="1" t="inlineStr">
+      <c r="Z16" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA17" s="1" t="inlineStr"/>
-      <c r="AB17" s="1" t="inlineStr">
+      <c r="AA16" s="1" t="inlineStr"/>
+      <c r="AB16" s="1" t="inlineStr">
         <is>
           <t>3200000</t>
         </is>
       </c>
-      <c r="AC17" s="1" t="inlineStr">
+      <c r="AC16" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD17" s="1" t="inlineStr">
+      <c r="AD16" s="1" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="AE17" s="1" t="inlineStr"/>
-      <c r="AF17" s="1" t="inlineStr">
+      <c r="AE16" s="1" t="inlineStr"/>
+      <c r="AF16" s="1" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="AG17" s="1" t="inlineStr">
+      <c r="AG16" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH17" s="1" t="inlineStr"/>
-      <c r="AI17" s="1" t="inlineStr">
+      <c r="AH16" s="1" t="inlineStr"/>
+      <c r="AI16" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ17" s="1" t="inlineStr"/>
-      <c r="AK17" s="1" t="inlineStr"/>
-      <c r="AL17" s="1" t="inlineStr"/>
-      <c r="AM17" s="1" t="inlineStr">
+      <c r="AJ16" s="1" t="inlineStr"/>
+      <c r="AK16" s="1" t="inlineStr"/>
+      <c r="AL16" s="1" t="inlineStr"/>
+      <c r="AM16" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN17" s="1" t="inlineStr"/>
-      <c r="AO17" s="1" t="inlineStr">
+      <c r="AN16" s="1" t="inlineStr"/>
+      <c r="AO16" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP17" s="1" t="inlineStr">
+      <c r="AP16" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ17" s="1" t="inlineStr">
+      <c r="AQ16" s="1" t="inlineStr">
         <is>
           <t>L3 (9445)</t>
         </is>
       </c>
-      <c r="AR17" s="1" t="inlineStr">
+      <c r="AR16" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS17" s="1" t="inlineStr">
+      <c r="AS16" s="1" t="inlineStr">
         <is>
           <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
-      <c r="AT17" s="1" t="inlineStr"/>
-      <c r="AU17" s="1" t="inlineStr"/>
-      <c r="AV17" s="1" t="inlineStr"/>
-      <c r="AW17" s="1" t="inlineStr">
+      <c r="AT16" s="1" t="inlineStr"/>
+      <c r="AU16" s="1" t="inlineStr"/>
+      <c r="AV16" s="1" t="inlineStr"/>
+      <c r="AW16" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX17" s="1" t="inlineStr">
+      <c r="AX16" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AY17" s="1" t="inlineStr">
+      <c r="AY16" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ17" s="1" t="inlineStr">
+      <c r="AZ16" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="BA17" s="1" t="inlineStr">
+      <c r="BA16" s="1" t="inlineStr">
         <is>
           <t>36700</t>
         </is>
       </c>
-      <c r="BB17" s="1" t="inlineStr">
+      <c r="BB16" s="1" t="inlineStr">
         <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="BC17" s="1" t="inlineStr">
+      <c r="BC16" s="1" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="BD17" s="1" t="inlineStr"/>
-      <c r="BE17" s="1" t="inlineStr"/>
+      <c r="BD16" s="1" t="inlineStr"/>
+      <c r="BE16" s="1" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>tonar-reef-r313</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr"/>
-      <c r="F18" s="1" t="inlineStr"/>
-      <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr"/>
-      <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+      <c r="G17" s="1" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="M17" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-рефрижератор Тонар R3-13, новый, под заказ у завода-изготовителя. 13,6 м, 3 оси, первая подъёмная, 33 европаллеты. Доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути.
 Поставка после согласования комплектации.
@@ -4008,189 +3819,189 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="N17" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O18" s="1" t="inlineStr">
+      <c r="O17" s="1" t="inlineStr">
         <is>
           <t>7365000</t>
         </is>
       </c>
-      <c r="P18" s="1" t="inlineStr"/>
-      <c r="Q18" s="1" t="inlineStr"/>
-      <c r="R18" s="1" t="inlineStr">
+      <c r="P17" s="1" t="inlineStr"/>
+      <c r="Q17" s="1" t="inlineStr"/>
+      <c r="R17" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg</t>
         </is>
       </c>
-      <c r="S18" s="1" t="inlineStr"/>
-      <c r="T18" s="1" t="inlineStr"/>
-      <c r="U18" s="1" t="inlineStr">
+      <c r="S17" s="1" t="inlineStr"/>
+      <c r="T17" s="1" t="inlineStr"/>
+      <c r="U17" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V18" s="1" t="inlineStr"/>
-      <c r="W18" s="1" t="inlineStr"/>
-      <c r="X18" s="1" t="inlineStr">
+      <c r="V17" s="1" t="inlineStr"/>
+      <c r="W17" s="1" t="inlineStr"/>
+      <c r="X17" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y18" s="1" t="inlineStr">
+      <c r="Y17" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
+      <c r="Z17" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA18" s="1" t="inlineStr"/>
-      <c r="AB18" s="1" t="inlineStr">
+      <c r="AA17" s="1" t="inlineStr"/>
+      <c r="AB17" s="1" t="inlineStr">
         <is>
           <t>7365000</t>
         </is>
       </c>
-      <c r="AC18" s="1" t="inlineStr">
+      <c r="AC17" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD18" s="1" t="inlineStr">
+      <c r="AD17" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AE18" s="1" t="inlineStr"/>
-      <c r="AF18" s="1" t="inlineStr"/>
-      <c r="AG18" s="1" t="inlineStr">
+      <c r="AE17" s="1" t="inlineStr"/>
+      <c r="AF17" s="1" t="inlineStr"/>
+      <c r="AG17" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH18" s="1" t="inlineStr"/>
-      <c r="AI18" s="1" t="inlineStr">
+      <c r="AH17" s="1" t="inlineStr"/>
+      <c r="AI17" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ18" s="1" t="inlineStr"/>
-      <c r="AK18" s="1" t="inlineStr"/>
-      <c r="AL18" s="1" t="inlineStr"/>
-      <c r="AM18" s="1" t="inlineStr">
+      <c r="AJ17" s="1" t="inlineStr"/>
+      <c r="AK17" s="1" t="inlineStr"/>
+      <c r="AL17" s="1" t="inlineStr"/>
+      <c r="AM17" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN18" s="1" t="inlineStr"/>
-      <c r="AO18" s="1" t="inlineStr">
+      <c r="AN17" s="1" t="inlineStr"/>
+      <c r="AO17" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP18" s="1" t="inlineStr">
+      <c r="AP17" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ18" s="1" t="inlineStr">
+      <c r="AQ17" s="1" t="inlineStr">
         <is>
           <t>R3-13</t>
         </is>
       </c>
-      <c r="AR18" s="1" t="inlineStr">
+      <c r="AR17" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS18" s="1" t="inlineStr">
+      <c r="AS17" s="1" t="inlineStr">
         <is>
           <t>Рефрижератор</t>
         </is>
       </c>
-      <c r="AT18" s="1" t="inlineStr"/>
-      <c r="AU18" s="1" t="inlineStr"/>
-      <c r="AV18" s="1" t="inlineStr"/>
-      <c r="AW18" s="1" t="inlineStr">
+      <c r="AT17" s="1" t="inlineStr"/>
+      <c r="AU17" s="1" t="inlineStr"/>
+      <c r="AV17" s="1" t="inlineStr"/>
+      <c r="AW17" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX18" s="1" t="inlineStr">
+      <c r="AX17" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AY18" s="1" t="inlineStr">
+      <c r="AY17" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ18" s="1" t="inlineStr">
+      <c r="AZ17" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA18" s="1" t="inlineStr">
+      <c r="BA17" s="1" t="inlineStr">
         <is>
           <t>31200</t>
         </is>
       </c>
-      <c r="BB18" s="1" t="inlineStr">
+      <c r="BB17" s="1" t="inlineStr">
         <is>
           <t>13600</t>
         </is>
       </c>
-      <c r="BC18" s="1" t="inlineStr">
+      <c r="BC17" s="1" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="BD18" s="1" t="inlineStr"/>
-      <c r="BE18" s="1" t="inlineStr"/>
+      <c r="BD17" s="1" t="inlineStr"/>
+      <c r="BE17" s="1" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>tonar-samosval-9595</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="inlineStr"/>
-      <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M19" s="1" t="inlineStr">
+      <c r="M18" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH4-34 (9595), новый, под заказ у завода-изготовителя. Задняя разгрузка, облегчённый, 4 оси, кузов 33,6 м³ полукруглой формы — сыпучий груз сходит легче, в том числе влажный. Под сыпучие строительные материалы.
 Поставка после согласования комплектации.
@@ -4214,189 +4025,189 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N19" s="1" t="inlineStr">
+      <c r="N18" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="O18" s="1" t="inlineStr">
         <is>
           <t>4200000</t>
         </is>
       </c>
-      <c r="P19" s="1" t="inlineStr"/>
-      <c r="Q19" s="1" t="inlineStr"/>
-      <c r="R19" s="1" t="inlineStr">
+      <c r="P18" s="1" t="inlineStr"/>
+      <c r="Q18" s="1" t="inlineStr"/>
+      <c r="R18" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
         </is>
       </c>
-      <c r="S19" s="1" t="inlineStr"/>
-      <c r="T19" s="1" t="inlineStr"/>
-      <c r="U19" s="1" t="inlineStr">
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="1" t="inlineStr"/>
+      <c r="U18" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V19" s="1" t="inlineStr"/>
-      <c r="W19" s="1" t="inlineStr"/>
-      <c r="X19" s="1" t="inlineStr">
+      <c r="V18" s="1" t="inlineStr"/>
+      <c r="W18" s="1" t="inlineStr"/>
+      <c r="X18" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y19" s="1" t="inlineStr">
+      <c r="Y18" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z19" s="1" t="inlineStr">
+      <c r="Z18" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA19" s="1" t="inlineStr"/>
-      <c r="AB19" s="1" t="inlineStr">
+      <c r="AA18" s="1" t="inlineStr"/>
+      <c r="AB18" s="1" t="inlineStr">
         <is>
           <t>4200000</t>
         </is>
       </c>
-      <c r="AC19" s="1" t="inlineStr">
+      <c r="AC18" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD19" s="1" t="inlineStr">
+      <c r="AD18" s="1" t="inlineStr">
         <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="AE19" s="1" t="inlineStr"/>
-      <c r="AF19" s="1" t="inlineStr"/>
-      <c r="AG19" s="1" t="inlineStr">
+      <c r="AE18" s="1" t="inlineStr"/>
+      <c r="AF18" s="1" t="inlineStr"/>
+      <c r="AG18" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH19" s="1" t="inlineStr"/>
-      <c r="AI19" s="1" t="inlineStr">
+      <c r="AH18" s="1" t="inlineStr"/>
+      <c r="AI18" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ19" s="1" t="inlineStr"/>
-      <c r="AK19" s="1" t="inlineStr"/>
-      <c r="AL19" s="1" t="inlineStr"/>
-      <c r="AM19" s="1" t="inlineStr">
+      <c r="AJ18" s="1" t="inlineStr"/>
+      <c r="AK18" s="1" t="inlineStr"/>
+      <c r="AL18" s="1" t="inlineStr"/>
+      <c r="AM18" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN19" s="1" t="inlineStr"/>
-      <c r="AO19" s="1" t="inlineStr">
+      <c r="AN18" s="1" t="inlineStr"/>
+      <c r="AO18" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP19" s="1" t="inlineStr">
+      <c r="AP18" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ19" s="1" t="inlineStr">
+      <c r="AQ18" s="1" t="inlineStr">
         <is>
           <t>9595</t>
         </is>
       </c>
-      <c r="AR19" s="1" t="inlineStr">
+      <c r="AR18" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS19" s="1" t="inlineStr">
+      <c r="AS18" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AT19" s="1" t="inlineStr"/>
-      <c r="AU19" s="1" t="inlineStr"/>
-      <c r="AV19" s="1" t="inlineStr"/>
-      <c r="AW19" s="1" t="inlineStr">
+      <c r="AT18" s="1" t="inlineStr"/>
+      <c r="AU18" s="1" t="inlineStr"/>
+      <c r="AV18" s="1" t="inlineStr"/>
+      <c r="AW18" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX19" s="1" t="inlineStr">
+      <c r="AX18" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY19" s="1" t="inlineStr">
+      <c r="AY18" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ19" s="1" t="inlineStr">
+      <c r="AZ18" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="BA19" s="1" t="inlineStr">
+      <c r="BA18" s="1" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="BB19" s="1" t="inlineStr">
+      <c r="BB18" s="1" t="inlineStr">
         <is>
           <t>10110</t>
         </is>
       </c>
-      <c r="BC19" s="1" t="inlineStr">
+      <c r="BC18" s="1" t="inlineStr">
         <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="BD19" s="1" t="inlineStr"/>
-      <c r="BE19" s="1" t="inlineStr"/>
+      <c r="BD18" s="1" t="inlineStr"/>
+      <c r="BE18" s="1" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>tonar-sdp489-95895</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="M19" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп со сдвижным полом Тонар SDP4-89 (95895), новый, под заказ у завода-изготовителя. Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без подъёма кузова — можно разгружаться на неровных площадках и под низкими навесами. Под насыпные грузы: щепа, зерно, песок и т. п.
 Поставка после согласования комплектации.
@@ -4415,189 +4226,189 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="N19" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="O19" s="1" t="inlineStr">
         <is>
           <t>7650000</t>
         </is>
       </c>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr">
+      <c r="P19" s="1" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr"/>
+      <c r="R19" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
         </is>
       </c>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr">
+      <c r="S19" s="1" t="inlineStr"/>
+      <c r="T19" s="1" t="inlineStr"/>
+      <c r="U19" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr">
+      <c r="V19" s="1" t="inlineStr"/>
+      <c r="W19" s="1" t="inlineStr"/>
+      <c r="X19" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y20" s="1" t="inlineStr">
+      <c r="Y19" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z20" s="1" t="inlineStr">
+      <c r="Z19" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA20" s="1" t="inlineStr"/>
-      <c r="AB20" s="1" t="inlineStr">
+      <c r="AA19" s="1" t="inlineStr"/>
+      <c r="AB19" s="1" t="inlineStr">
         <is>
           <t>7650000</t>
         </is>
       </c>
-      <c r="AC20" s="1" t="inlineStr">
+      <c r="AC19" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD20" s="1" t="inlineStr">
+      <c r="AD19" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AE20" s="1" t="inlineStr"/>
-      <c r="AF20" s="1" t="inlineStr"/>
-      <c r="AG20" s="1" t="inlineStr">
+      <c r="AE19" s="1" t="inlineStr"/>
+      <c r="AF19" s="1" t="inlineStr"/>
+      <c r="AG19" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH20" s="1" t="inlineStr"/>
-      <c r="AI20" s="1" t="inlineStr">
+      <c r="AH19" s="1" t="inlineStr"/>
+      <c r="AI19" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ20" s="1" t="inlineStr"/>
-      <c r="AK20" s="1" t="inlineStr"/>
-      <c r="AL20" s="1" t="inlineStr"/>
-      <c r="AM20" s="1" t="inlineStr">
+      <c r="AJ19" s="1" t="inlineStr"/>
+      <c r="AK19" s="1" t="inlineStr"/>
+      <c r="AL19" s="1" t="inlineStr"/>
+      <c r="AM19" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN20" s="1" t="inlineStr"/>
-      <c r="AO20" s="1" t="inlineStr">
+      <c r="AN19" s="1" t="inlineStr"/>
+      <c r="AO19" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP20" s="1" t="inlineStr">
+      <c r="AP19" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ20" s="1" t="inlineStr">
+      <c r="AQ19" s="1" t="inlineStr">
         <is>
           <t>SDP4-89 (95895)</t>
         </is>
       </c>
-      <c r="AR20" s="1" t="inlineStr">
+      <c r="AR19" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS20" s="1" t="inlineStr">
+      <c r="AS19" s="1" t="inlineStr">
         <is>
           <t>Щеповоз</t>
         </is>
       </c>
-      <c r="AT20" s="1" t="inlineStr"/>
-      <c r="AU20" s="1" t="inlineStr"/>
-      <c r="AV20" s="1" t="inlineStr"/>
-      <c r="AW20" s="1" t="inlineStr">
+      <c r="AT19" s="1" t="inlineStr"/>
+      <c r="AU19" s="1" t="inlineStr"/>
+      <c r="AV19" s="1" t="inlineStr"/>
+      <c r="AW19" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX20" s="1" t="inlineStr">
+      <c r="AX19" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AY20" s="1" t="inlineStr">
+      <c r="AY19" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ20" s="1" t="inlineStr">
+      <c r="AZ19" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA20" s="1" t="inlineStr">
+      <c r="BA19" s="1" t="inlineStr">
         <is>
           <t>27800</t>
         </is>
       </c>
-      <c r="BB20" s="1" t="inlineStr">
+      <c r="BB19" s="1" t="inlineStr">
         <is>
           <t>14600</t>
         </is>
       </c>
-      <c r="BC20" s="1" t="inlineStr">
+      <c r="BC19" s="1" t="inlineStr">
         <is>
           <t>89.6</t>
         </is>
       </c>
-      <c r="BD20" s="1" t="inlineStr"/>
-      <c r="BE20" s="1" t="inlineStr"/>
+      <c r="BD19" s="1" t="inlineStr"/>
+      <c r="BE19" s="1" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>tonar-t313-9888</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="M20" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), новый, под заказ у завода-изготовителя. 13,6 м, 3 оси, первая подъёмная, со стаканами под коники (коники в комплект не входят).
 Поставка после согласования комплектации.
@@ -4624,193 +4435,193 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
+      <c r="N20" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr">
         <is>
           <t>3800000</t>
         </is>
       </c>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr">
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
         </is>
       </c>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr">
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr">
+      <c r="V20" s="1" t="inlineStr"/>
+      <c r="W20" s="1" t="inlineStr"/>
+      <c r="X20" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y21" s="1" t="inlineStr">
+      <c r="Y20" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z21" s="1" t="inlineStr">
+      <c r="Z20" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA21" s="1" t="inlineStr"/>
-      <c r="AB21" s="1" t="inlineStr">
+      <c r="AA20" s="1" t="inlineStr"/>
+      <c r="AB20" s="1" t="inlineStr">
         <is>
           <t>3800000</t>
         </is>
       </c>
-      <c r="AC21" s="1" t="inlineStr">
+      <c r="AC20" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD21" s="1" t="inlineStr">
+      <c r="AD20" s="1" t="inlineStr">
         <is>
           <t>380000</t>
         </is>
       </c>
-      <c r="AE21" s="1" t="inlineStr"/>
-      <c r="AF21" s="1" t="inlineStr">
+      <c r="AE20" s="1" t="inlineStr"/>
+      <c r="AF20" s="1" t="inlineStr">
         <is>
           <t>380000</t>
         </is>
       </c>
-      <c r="AG21" s="1" t="inlineStr">
+      <c r="AG20" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH21" s="1" t="inlineStr"/>
-      <c r="AI21" s="1" t="inlineStr">
+      <c r="AH20" s="1" t="inlineStr"/>
+      <c r="AI20" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ21" s="1" t="inlineStr"/>
-      <c r="AK21" s="1" t="inlineStr"/>
-      <c r="AL21" s="1" t="inlineStr"/>
-      <c r="AM21" s="1" t="inlineStr">
+      <c r="AJ20" s="1" t="inlineStr"/>
+      <c r="AK20" s="1" t="inlineStr"/>
+      <c r="AL20" s="1" t="inlineStr"/>
+      <c r="AM20" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN21" s="1" t="inlineStr"/>
-      <c r="AO21" s="1" t="inlineStr">
+      <c r="AN20" s="1" t="inlineStr"/>
+      <c r="AO20" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP21" s="1" t="inlineStr">
+      <c r="AP20" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ21" s="1" t="inlineStr">
+      <c r="AQ20" s="1" t="inlineStr">
         <is>
           <t>T3-13 (9888)</t>
         </is>
       </c>
-      <c r="AR21" s="1" t="inlineStr">
+      <c r="AR20" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS21" s="1" t="inlineStr">
+      <c r="AS20" s="1" t="inlineStr">
         <is>
           <t>Шторно-бортовой</t>
         </is>
       </c>
-      <c r="AT21" s="1" t="inlineStr"/>
-      <c r="AU21" s="1" t="inlineStr"/>
-      <c r="AV21" s="1" t="inlineStr"/>
-      <c r="AW21" s="1" t="inlineStr">
+      <c r="AT20" s="1" t="inlineStr"/>
+      <c r="AU20" s="1" t="inlineStr"/>
+      <c r="AV20" s="1" t="inlineStr"/>
+      <c r="AW20" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX21" s="1" t="inlineStr">
+      <c r="AX20" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AY21" s="1" t="inlineStr">
+      <c r="AY20" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ21" s="1" t="inlineStr">
+      <c r="AZ20" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA21" s="1" t="inlineStr">
+      <c r="BA20" s="1" t="inlineStr">
         <is>
           <t>31000</t>
         </is>
       </c>
-      <c r="BB21" s="1" t="inlineStr">
+      <c r="BB20" s="1" t="inlineStr">
         <is>
           <t>13600</t>
         </is>
       </c>
-      <c r="BC21" s="1" t="inlineStr">
+      <c r="BC20" s="1" t="inlineStr">
         <is>
           <t>91.4</t>
         </is>
       </c>
-      <c r="BD21" s="1" t="inlineStr"/>
-      <c r="BE21" s="1" t="inlineStr"/>
+      <c r="BD20" s="1" t="inlineStr"/>
+      <c r="BE20" s="1" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>tonar-zernovoz-95941</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="M21" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп-зерновоз Тонар 95941, новый, под заказ у завода-изготовителя. Задняя разгрузка, алюминиевый прямоугольный кузов 50 м³, до 33,2 т груза, 3 оси (первая подъёмная). Насыпные зерновые, комбикорм и паллетированный груз.
 Поставка после согласования комплектации.
@@ -4835,189 +4646,189 @@
 Позвоните или напишите — рассчитаем платёж по лизингу и срок поставки.</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>5400000</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
-      <c r="R22" s="1" t="inlineStr">
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr"/>
+      <c r="R21" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
         </is>
       </c>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
-      <c r="U22" s="1" t="inlineStr">
+      <c r="S21" s="1" t="inlineStr"/>
+      <c r="T21" s="1" t="inlineStr"/>
+      <c r="U21" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V22" s="1" t="inlineStr"/>
-      <c r="W22" s="1" t="inlineStr"/>
-      <c r="X22" s="1" t="inlineStr">
+      <c r="V21" s="1" t="inlineStr"/>
+      <c r="W21" s="1" t="inlineStr"/>
+      <c r="X21" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y22" s="1" t="inlineStr">
+      <c r="Y21" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z22" s="1" t="inlineStr">
+      <c r="Z21" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA22" s="1" t="inlineStr"/>
-      <c r="AB22" s="1" t="inlineStr">
+      <c r="AA21" s="1" t="inlineStr"/>
+      <c r="AB21" s="1" t="inlineStr">
         <is>
           <t>5400000</t>
         </is>
       </c>
-      <c r="AC22" s="1" t="inlineStr">
+      <c r="AC21" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD22" s="1" t="inlineStr">
+      <c r="AD21" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AE22" s="1" t="inlineStr"/>
-      <c r="AF22" s="1" t="inlineStr"/>
-      <c r="AG22" s="1" t="inlineStr">
+      <c r="AE21" s="1" t="inlineStr"/>
+      <c r="AF21" s="1" t="inlineStr"/>
+      <c r="AG21" s="1" t="inlineStr">
         <is>
           <t>Платная</t>
         </is>
       </c>
-      <c r="AH22" s="1" t="inlineStr"/>
-      <c r="AI22" s="1" t="inlineStr">
+      <c r="AH21" s="1" t="inlineStr"/>
+      <c r="AI21" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AJ22" s="1" t="inlineStr"/>
-      <c r="AK22" s="1" t="inlineStr"/>
-      <c r="AL22" s="1" t="inlineStr"/>
-      <c r="AM22" s="1" t="inlineStr">
+      <c r="AJ21" s="1" t="inlineStr"/>
+      <c r="AK21" s="1" t="inlineStr"/>
+      <c r="AL21" s="1" t="inlineStr"/>
+      <c r="AM21" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AN22" s="1" t="inlineStr"/>
-      <c r="AO22" s="1" t="inlineStr">
+      <c r="AN21" s="1" t="inlineStr"/>
+      <c r="AO21" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP22" s="1" t="inlineStr">
+      <c r="AP21" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AQ22" s="1" t="inlineStr">
+      <c r="AQ21" s="1" t="inlineStr">
         <is>
           <t>95941</t>
         </is>
       </c>
-      <c r="AR22" s="1" t="inlineStr">
+      <c r="AR21" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS22" s="1" t="inlineStr">
+      <c r="AS21" s="1" t="inlineStr">
         <is>
           <t>Зерновоз</t>
         </is>
       </c>
-      <c r="AT22" s="1" t="inlineStr"/>
-      <c r="AU22" s="1" t="inlineStr"/>
-      <c r="AV22" s="1" t="inlineStr"/>
-      <c r="AW22" s="1" t="inlineStr">
+      <c r="AT21" s="1" t="inlineStr"/>
+      <c r="AU21" s="1" t="inlineStr"/>
+      <c r="AV21" s="1" t="inlineStr"/>
+      <c r="AW21" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AX22" s="1" t="inlineStr">
+      <c r="AX21" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AY22" s="1" t="inlineStr">
+      <c r="AY21" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ22" s="1" t="inlineStr">
+      <c r="AZ21" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="BA22" s="1" t="inlineStr">
+      <c r="BA21" s="1" t="inlineStr">
         <is>
           <t>33200</t>
         </is>
       </c>
-      <c r="BB22" s="1" t="inlineStr">
+      <c r="BB21" s="1" t="inlineStr">
         <is>
           <t>12166</t>
         </is>
       </c>
-      <c r="BC22" s="1" t="inlineStr">
+      <c r="BC21" s="1" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="BD22" s="1" t="inlineStr"/>
-      <c r="BE22" s="1" t="inlineStr"/>
+      <c r="BD21" s="1" t="inlineStr"/>
+      <c r="BE21" s="1" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>55.8958019</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>37.5237956</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>v-trailer-329d-r0000119</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+      <c r="G22" s="1" t="inlineStr"/>
+      <c r="H22" s="1" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr"/>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr">
         <is>
           <t>79685590315</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="M22" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп шторный V-Trailer 329D, 2023 года, б/у. В работе, полностью исправен.
 Осмотр: Москва, Ижорская ул., 15с2.
@@ -5037,142 +4848,142 @@
 Позвоните или напишите — пришлём VIN, рассчитаем платёж по лизингу.</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="N22" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="O22" s="1" t="inlineStr">
         <is>
           <t>2990000</t>
         </is>
       </c>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr">
+      <c r="P22" s="1" t="inlineStr"/>
+      <c r="Q22" s="1" t="inlineStr"/>
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
         </is>
       </c>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
-      <c r="U23" s="1" t="inlineStr">
+      <c r="S22" s="1" t="inlineStr"/>
+      <c r="T22" s="1" t="inlineStr"/>
+      <c r="U22" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="V23" s="1" t="inlineStr"/>
-      <c r="W23" s="1" t="inlineStr"/>
-      <c r="X23" s="1" t="inlineStr">
+      <c r="V22" s="1" t="inlineStr"/>
+      <c r="W22" s="1" t="inlineStr"/>
+      <c r="X22" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="Y23" s="1" t="inlineStr">
+      <c r="Y22" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="Z23" s="1" t="inlineStr">
+      <c r="Z22" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AA23" s="1" t="inlineStr"/>
-      <c r="AB23" s="1" t="inlineStr">
+      <c r="AA22" s="1" t="inlineStr"/>
+      <c r="AB22" s="1" t="inlineStr">
         <is>
           <t>2990000</t>
         </is>
       </c>
-      <c r="AC23" s="1" t="inlineStr">
+      <c r="AC22" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD23" s="1" t="inlineStr"/>
-      <c r="AE23" s="1" t="inlineStr"/>
-      <c r="AF23" s="1" t="inlineStr"/>
-      <c r="AG23" s="1" t="inlineStr"/>
-      <c r="AH23" s="1" t="inlineStr"/>
-      <c r="AI23" s="1" t="inlineStr"/>
-      <c r="AJ23" s="1" t="inlineStr"/>
-      <c r="AK23" s="1" t="inlineStr"/>
-      <c r="AL23" s="1" t="inlineStr"/>
-      <c r="AM23" s="1" t="inlineStr">
+      <c r="AD22" s="1" t="inlineStr"/>
+      <c r="AE22" s="1" t="inlineStr"/>
+      <c r="AF22" s="1" t="inlineStr"/>
+      <c r="AG22" s="1" t="inlineStr"/>
+      <c r="AH22" s="1" t="inlineStr"/>
+      <c r="AI22" s="1" t="inlineStr"/>
+      <c r="AJ22" s="1" t="inlineStr"/>
+      <c r="AK22" s="1" t="inlineStr"/>
+      <c r="AL22" s="1" t="inlineStr"/>
+      <c r="AM22" s="1" t="inlineStr">
         <is>
           <t>С пробегом</t>
         </is>
       </c>
-      <c r="AN23" s="1" t="inlineStr"/>
-      <c r="AO23" s="1" t="inlineStr">
+      <c r="AN22" s="1" t="inlineStr"/>
+      <c r="AO22" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AP23" s="1" t="inlineStr">
+      <c r="AP22" s="1" t="inlineStr">
         <is>
           <t>V-Trailer</t>
         </is>
       </c>
-      <c r="AQ23" s="1" t="inlineStr">
+      <c r="AQ22" s="1" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="AR23" s="1" t="inlineStr">
+      <c r="AR22" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AS23" s="1" t="inlineStr">
+      <c r="AS22" s="1" t="inlineStr">
         <is>
           <t>Шторный</t>
         </is>
       </c>
-      <c r="AT23" s="1" t="inlineStr"/>
-      <c r="AU23" s="1" t="inlineStr"/>
-      <c r="AV23" s="1" t="inlineStr">
+      <c r="AT22" s="1" t="inlineStr"/>
+      <c r="AU22" s="1" t="inlineStr"/>
+      <c r="AV22" s="1" t="inlineStr">
         <is>
           <t>XZFVKRP3DR0000119</t>
         </is>
       </c>
-      <c r="AW23" s="1" t="inlineStr">
+      <c r="AW22" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AX23" s="1" t="inlineStr">
+      <c r="AX22" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AY23" s="1" t="inlineStr">
+      <c r="AY22" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ23" s="1" t="inlineStr">
+      <c r="AZ22" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA23" s="1" t="inlineStr">
+      <c r="BA22" s="1" t="inlineStr">
         <is>
           <t>32300</t>
         </is>
       </c>
-      <c r="BB23" s="1" t="inlineStr">
+      <c r="BB22" s="1" t="inlineStr">
         <is>
           <t>13600</t>
         </is>
       </c>
-      <c r="BC23" s="1" t="inlineStr">
+      <c r="BC22" s="1" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="BD23" s="1" t="inlineStr"/>
-      <c r="BE23" s="1" t="inlineStr"/>
+      <c r="BD22" s="1" t="inlineStr"/>
+      <c r="BE22" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -808,7 +808,6 @@
 — гарантия 24 месяца без ограничения пробега;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси барабанные, 12 т, L1 (Китай); пневмоподвеска с подъёмом 1-й и 2-й осей;
@@ -1018,8 +1017,7 @@
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — возможна аренда с правом выкупа;
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
 Технические характеристики
 — оси: 4 (3 + выносная балансирная), с подъёмом осей;
 — подвеска пневматическая; тормоза дисковые, ABS SORL;
@@ -1208,7 +1206,6 @@
 Условия
 — возможна аренда с правом выкупа;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами;
 — торг при осмотре.
 Технические характеристики
 — оси BPW, 3 шт.; подвеска зависимая, на продольных рычагах; тормоза дисковые;
@@ -1401,7 +1398,6 @@
 Условия
 — возможна аренда с правом выкупа;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами;
 — торг при осмотре.
 Технические характеристики
 — оси BPW, 3 шт.; подвеска зависимая, на продольных рычагах; тормоза дисковые;
@@ -1594,7 +1590,6 @@
 Условия
 — возможна аренда с правом выкупа;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами;
 — торг при осмотре.
 Технические характеристики
 — оси BPW, 3 шт.; подвеска рессорная; тормоза барабанные;
@@ -1785,8 +1780,7 @@
           <t>Полуприцеп-контейнеровоз Makinsan L4, универсальная платформа, 2023 года, б/у. В работе, полностью исправен.
 Осмотр: Ставропольский край, с. Надежда, ул. Ставропольская, 83.
 Условия
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
 Технические характеристики
 — оси SAF Intradisc 4 × 9 т, дисковые тормоза;
 — пневмоподвеска с подъёмом передней и задней оси;
@@ -1979,7 +1973,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — контейнеры: 1 × 40' (в т. ч. HQ), 2 × 20' или 1 × 20' по центру;
@@ -2180,7 +2173,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — осевой агрегат Fox, барабанные тормоза, нагрузка на ось 9 000 кг;
@@ -2383,7 +2375,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — борт алюминиевый; боковые борта откидные, 8 шт.; задний — откидной; передний — металлический, съёмный;
@@ -2588,7 +2579,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, 1-я и 2-я подъёмные;
@@ -2791,8 +2781,7 @@
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — возможна аренда с правом выкупа;
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось;
 — тормоза дисковые, пневмопривод;
@@ -2984,7 +2973,6 @@
 — акция до 31 октября — уточняйте условия у менеджера;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
@@ -3187,7 +3175,6 @@
 — акция до 31 октября — уточняйте условия у менеджера;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
@@ -3390,7 +3377,6 @@
 — акция до 31 октября — уточняйте условия у менеджера;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
@@ -3593,7 +3579,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — геометрический объём перевозимого груза 63 м³;
@@ -3802,7 +3787,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — кузов из сэндвич-панелей, объём 86,9 м³; пол герметичный, из сэндвич-панели, настил — рифлёный алюминий;
@@ -4010,7 +3994,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — тент с механическим приводом в базовой комплектации; задний борт откидной, с лючком регулировки разгрузки;
@@ -4216,7 +4199,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, первая вынесенная;
@@ -4418,7 +4400,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — крыша сдвижная, с возможностью верхней загрузки; боковины — шторы и алюминиевые борта, 8 шт.;
@@ -4630,7 +4611,6 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
-— работаем с юридическими и физическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — тент с механическим приводом в базовой комплектации;
@@ -4834,8 +4814,7 @@
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — возможна аренда с правом выкупа;
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
-— работаем с юридическими и физическими лицами.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
 Технические характеристики
 — 13,6 × 2,5 × 4 м, 91 м³; полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте;
 — оси SAF, передняя подъёмная;

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -808,6 +808,7 @@
 — гарантия 24 месяца без ограничения пробега;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси барабанные, 12 т, L1 (Китай); пневмоподвеска с подъёмом 1-й и 2-й осей;
@@ -1017,7 +1018,8 @@
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — возможна аренда с правом выкупа;
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами.
 Технические характеристики
 — оси: 4 (3 + выносная балансирная), с подъёмом осей;
 — подвеска пневматическая; тормоза дисковые, ABS SORL;
@@ -1206,6 +1208,7 @@
 Условия
 — возможна аренда с правом выкупа;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами;
 — торг при осмотре.
 Технические характеристики
 — оси BPW, 3 шт.; подвеска зависимая, на продольных рычагах; тормоза дисковые;
@@ -1398,6 +1401,7 @@
 Условия
 — возможна аренда с правом выкупа;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами;
 — торг при осмотре.
 Технические характеристики
 — оси BPW, 3 шт.; подвеска зависимая, на продольных рычагах; тормоза дисковые;
@@ -1590,6 +1594,7 @@
 Условия
 — возможна аренда с правом выкупа;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами;
 — торг при осмотре.
 Технические характеристики
 — оси BPW, 3 шт.; подвеска рессорная; тормоза барабанные;
@@ -1780,7 +1785,8 @@
           <t>Полуприцеп-контейнеровоз Makinsan L4, универсальная платформа, 2023 года, б/у. В работе, полностью исправен.
 Осмотр: Ставропольский край, с. Надежда, ул. Ставропольская, 83.
 Условия
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами.
 Технические характеристики
 — оси SAF Intradisc 4 × 9 т, дисковые тормоза;
 — пневмоподвеска с подъёмом передней и задней оси;
@@ -1973,6 +1979,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — контейнеры: 1 × 40' (в т. ч. HQ), 2 × 20' или 1 × 20' по центру;
@@ -2173,6 +2180,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — осевой агрегат Fox, барабанные тормоза, нагрузка на ось 9 000 кг;
@@ -2375,6 +2383,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — борт алюминиевый; боковые борта откидные, 8 шт.; задний — откидной; передний — металлический, съёмный;
@@ -2579,6 +2588,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, 1-я и 2-я подъёмные;
@@ -2781,7 +2791,8 @@
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — возможна аренда с правом выкупа;
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами.
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось;
 — тормоза дисковые, пневмопривод;
@@ -2973,6 +2984,7 @@
 — акция до 31 октября — уточняйте условия у менеджера;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
@@ -3175,6 +3187,7 @@
 — акция до 31 октября — уточняйте условия у менеджера;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
@@ -3377,6 +3390,7 @@
 — акция до 31 октября — уточняйте условия у менеджера;
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, тройная задняя тележка и вынесенная вперёд ось; 1-я и 2-я подъёмные;
@@ -3579,6 +3593,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — геометрический объём перевозимого груза 63 м³;
@@ -3787,6 +3802,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — кузов из сэндвич-панелей, объём 86,9 м³; пол герметичный, из сэндвич-панели, настил — рифлёный алюминий;
@@ -3994,6 +4010,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — тент с механическим приводом в базовой комплектации; задний борт откидной, с лючком регулировки разгрузки;
@@ -4199,6 +4216,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — оси: 4, первая вынесенная;
@@ -4400,6 +4418,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (коники, инструментальный ящик, запасное колесо, стальная обрешётка, сертификат на ТО и др.).
 Технические характеристики
 — крыша сдвижная, с возможностью верхней загрузки; боковины — шторы и алюминиевые борта, 8 шт.;
@@ -4611,6 +4630,7 @@
 — при покупке в лизинг — субсидия Минпромторга 10% (не более 500 000 ₽);
 — покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
 — доставка по России;
+— работаем с юридическими лицами;
 — подарок при покупке — уточняйте у менеджера (инструментальный ящик, запасное колесо, сертификат на ТО и др.).
 Технические характеристики
 — тент с механическим приводом в базовой комплектации;
@@ -4814,7 +4834,8 @@
 Осмотр: Москва, Ижорская ул., 15с2.
 Условия
 — возможна аренда с правом выкупа;
-— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.
+— покупка в лизинг через партнёров: Европлан, ВТБ Лизинг, Сберлизинг, Газпромбанк Лизинг, РЕСО Лизинг и др.;
+— работаем с юридическими лицами.
 Технические характеристики
 — 13,6 × 2,5 × 4 м, 91 м³; полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте;
 — оси SAF, передняя подъёмная;

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>1890000</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
       <c r="AA12" s="1" t="inlineStr"/>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>1890000</t>
         </is>
       </c>
       <c r="AC12" s="1" t="inlineStr">
